--- a/data/resultats_xlsx.xlsx
+++ b/data/resultats_xlsx.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="207">
   <si>
     <t xml:space="preserve">EPREUVE</t>
   </si>
@@ -579,6 +579,57 @@
   </si>
   <si>
     <t xml:space="preserve">01:28.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:46.91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:57.69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:41.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:58.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:00.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 Brasse Dames</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02:02.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:46.42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:50.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:51.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:56.42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:50.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:56.96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:57.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:01.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:02.13</t>
   </si>
   <si>
     <t xml:space="preserve">NOM_PRENOM</t>
@@ -3584,25 +3635,25 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
+      <c r="A101" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B101" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C101" s="0" t="s">
+      <c r="B101" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D101" s="0" t="n">
+      <c r="D101" s="1" t="n">
         <v>2013</v>
       </c>
-      <c r="E101" s="0" t="s">
+      <c r="E101" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F101" s="4" t="s">
+      <c r="F101" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G101" s="0" t="n">
+      <c r="G101" s="1" t="n">
         <v>472</v>
       </c>
       <c r="H101" s="1" t="str">
@@ -3611,25 +3662,25 @@
       </c>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
+      <c r="A102" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B102" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C102" s="0" t="s">
+      <c r="B102" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D102" s="0" t="n">
+      <c r="D102" s="1" t="n">
         <v>2013</v>
       </c>
-      <c r="E102" s="0" t="s">
+      <c r="E102" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F102" s="4" t="s">
+      <c r="F102" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G102" s="0" t="n">
+      <c r="G102" s="1" t="n">
         <v>391</v>
       </c>
       <c r="H102" s="1" t="str">
@@ -3638,25 +3689,25 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="s">
+      <c r="A103" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B103" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C103" s="0" t="s">
+      <c r="B103" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D103" s="0" t="n">
+      <c r="D103" s="1" t="n">
         <v>2010</v>
       </c>
-      <c r="E103" s="0" t="s">
+      <c r="E103" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F103" s="4" t="s">
+      <c r="F103" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G103" s="0" t="n">
+      <c r="G103" s="1" t="n">
         <v>244</v>
       </c>
       <c r="H103" s="1" t="str">
@@ -3665,25 +3716,25 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
+      <c r="A104" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B104" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C104" s="0" t="s">
+      <c r="B104" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D104" s="0" t="n">
+      <c r="D104" s="1" t="n">
         <v>2014</v>
       </c>
-      <c r="E104" s="0" t="s">
+      <c r="E104" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F104" s="4" t="s">
+      <c r="F104" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G104" s="0" t="n">
+      <c r="G104" s="1" t="n">
         <v>84</v>
       </c>
       <c r="H104" s="1" t="str">
@@ -3692,25 +3743,25 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
+      <c r="A105" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B105" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C105" s="0" t="s">
+      <c r="B105" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D105" s="0" t="n">
+      <c r="D105" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E105" s="0" t="s">
+      <c r="E105" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="F105" s="4" t="s">
+      <c r="F105" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G105" s="0" t="n">
+      <c r="G105" s="1" t="n">
         <v>321</v>
       </c>
       <c r="H105" s="1" t="str">
@@ -3719,25 +3770,25 @@
       </c>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0" t="s">
+      <c r="A106" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B106" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C106" s="0" t="s">
+      <c r="B106" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D106" s="0" t="n">
+      <c r="D106" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E106" s="0" t="s">
+      <c r="E106" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F106" s="4" t="s">
+      <c r="F106" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G106" s="0" t="n">
+      <c r="G106" s="1" t="n">
         <v>499</v>
       </c>
       <c r="H106" s="1" t="str">
@@ -3746,25 +3797,25 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="s">
+      <c r="A107" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B107" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C107" s="0" t="s">
+      <c r="B107" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D107" s="0" t="n">
+      <c r="D107" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E107" s="0" t="s">
+      <c r="E107" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="F107" s="4" t="s">
+      <c r="F107" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G107" s="0" t="n">
+      <c r="G107" s="1" t="n">
         <v>486</v>
       </c>
       <c r="H107" s="1" t="str">
@@ -3773,25 +3824,25 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="0" t="s">
+      <c r="A108" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B108" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C108" s="0" t="s">
+      <c r="B108" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D108" s="0" t="n">
+      <c r="D108" s="1" t="n">
         <v>2014</v>
       </c>
-      <c r="E108" s="0" t="s">
+      <c r="E108" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="F108" s="4" t="s">
+      <c r="F108" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G108" s="0" t="n">
+      <c r="G108" s="1" t="n">
         <v>264</v>
       </c>
       <c r="H108" s="1" t="str">
@@ -3800,25 +3851,25 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="0" t="s">
+      <c r="A109" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B109" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C109" s="0" t="s">
+      <c r="B109" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D109" s="0" t="n">
+      <c r="D109" s="1" t="n">
         <v>2013</v>
       </c>
-      <c r="E109" s="0" t="s">
+      <c r="E109" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="F109" s="4" t="s">
+      <c r="F109" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G109" s="0" t="n">
+      <c r="G109" s="1" t="n">
         <v>134</v>
       </c>
       <c r="H109" s="1" t="str">
@@ -3827,25 +3878,25 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0" t="s">
+      <c r="A110" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B110" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C110" s="0" t="s">
+      <c r="B110" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D110" s="0" t="n">
+      <c r="D110" s="1" t="n">
         <v>2010</v>
       </c>
-      <c r="E110" s="0" t="s">
+      <c r="E110" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F110" s="4" t="s">
+      <c r="F110" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G110" s="0" t="n">
+      <c r="G110" s="1" t="n">
         <v>60</v>
       </c>
       <c r="H110" s="1" t="str">
@@ -3854,25 +3905,25 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0" t="s">
+      <c r="A111" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B111" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C111" s="0" t="s">
+      <c r="B111" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D111" s="0" t="n">
+      <c r="D111" s="1" t="n">
         <v>2008</v>
       </c>
-      <c r="E111" s="0" t="s">
+      <c r="E111" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F111" s="4" t="s">
+      <c r="F111" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G111" s="0" t="n">
+      <c r="G111" s="1" t="n">
         <v>460</v>
       </c>
       <c r="H111" s="1" t="str">
@@ -3881,25 +3932,25 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="0" t="s">
+      <c r="A112" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B112" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C112" s="0" t="s">
+      <c r="B112" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D112" s="0" t="n">
+      <c r="D112" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E112" s="0" t="s">
+      <c r="E112" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F112" s="4" t="s">
+      <c r="F112" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G112" s="0" t="n">
+      <c r="G112" s="1" t="n">
         <v>235</v>
       </c>
       <c r="H112" s="1" t="str">
@@ -3908,31 +3959,469 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0" t="s">
+      <c r="A113" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B113" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C113" s="0" t="s">
+      <c r="B113" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D113" s="0" t="n">
+      <c r="D113" s="1" t="n">
         <v>2008</v>
       </c>
-      <c r="E113" s="0" t="s">
+      <c r="E113" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F113" s="4" t="s">
+      <c r="F113" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G113" s="0" t="n">
+      <c r="G113" s="1" t="n">
         <v>460</v>
       </c>
       <c r="H113" s="1" t="str">
         <f aca="false">IF((YEAR(F113)-D113)&lt;=11,"Avenirs",IF((YEAR(F113)-D113)&lt;=13,"Benjamins",IF((YEAR(F113)-D113)&lt;=18,"Juniors",IF((YEAR(F113)-D113)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F113)-D113-25)/5,0)))))</f>
         <v>Juniors</v>
       </c>
+    </row>
+    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C114" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="D114" s="0" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E114" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G114" s="0" t="n">
+        <v>169</v>
+      </c>
+      <c r="H114" s="1" t="str">
+        <f aca="false">IF((YEAR(F114)-D114)&lt;=11,"Avenirs",IF((YEAR(F114)-D114)&lt;=13,"Benjamins",IF((YEAR(F114)-D114)&lt;=18,"Juniors",IF((YEAR(F114)-D114)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F114)-D114-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C115" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="D115" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E115" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G115" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H115" s="1" t="str">
+        <f aca="false">IF((YEAR(F115)-D115)&lt;=11,"Avenirs",IF((YEAR(F115)-D115)&lt;=13,"Benjamins",IF((YEAR(F115)-D115)&lt;=18,"Juniors",IF((YEAR(F115)-D115)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F115)-D115-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C116" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="D116" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E116" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G116" s="0" t="n">
+        <v>141</v>
+      </c>
+      <c r="H116" s="1" t="str">
+        <f aca="false">IF((YEAR(F116)-D116)&lt;=11,"Avenirs",IF((YEAR(F116)-D116)&lt;=13,"Benjamins",IF((YEAR(F116)-D116)&lt;=18,"Juniors",IF((YEAR(F116)-D116)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F116)-D116-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C117" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="D117" s="0" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E117" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G117" s="0" t="n">
+        <v>123</v>
+      </c>
+      <c r="H117" s="1" t="str">
+        <f aca="false">IF((YEAR(F117)-D117)&lt;=11,"Avenirs",IF((YEAR(F117)-D117)&lt;=13,"Benjamins",IF((YEAR(F117)-D117)&lt;=18,"Juniors",IF((YEAR(F117)-D117)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F117)-D117-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C118" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="D118" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E118" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G118" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="H118" s="1" t="str">
+        <f aca="false">IF((YEAR(F118)-D118)&lt;=11,"Avenirs",IF((YEAR(F118)-D118)&lt;=13,"Benjamins",IF((YEAR(F118)-D118)&lt;=18,"Juniors",IF((YEAR(F118)-D118)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F118)-D118-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C119" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="D119" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E119" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G119" s="0" t="n">
+        <v>299</v>
+      </c>
+      <c r="H119" s="1" t="str">
+        <f aca="false">IF((YEAR(F119)-D119)&lt;=11,"Avenirs",IF((YEAR(F119)-D119)&lt;=13,"Benjamins",IF((YEAR(F119)-D119)&lt;=18,"Juniors",IF((YEAR(F119)-D119)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F119)-D119-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C120" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="D120" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E120" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G120" s="0" t="n">
+        <v>246</v>
+      </c>
+      <c r="H120" s="1" t="str">
+        <f aca="false">IF((YEAR(F120)-D120)&lt;=11,"Avenirs",IF((YEAR(F120)-D120)&lt;=13,"Benjamins",IF((YEAR(F120)-D120)&lt;=18,"Juniors",IF((YEAR(F120)-D120)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F120)-D120-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C121" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="D121" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E121" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G121" s="0" t="n">
+        <v>121</v>
+      </c>
+      <c r="H121" s="1" t="str">
+        <f aca="false">IF((YEAR(F121)-D121)&lt;=11,"Avenirs",IF((YEAR(F121)-D121)&lt;=13,"Benjamins",IF((YEAR(F121)-D121)&lt;=18,"Juniors",IF((YEAR(F121)-D121)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F121)-D121-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C122" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="D122" s="0" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E122" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G122" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="H122" s="1" t="str">
+        <f aca="false">IF((YEAR(F122)-D122)&lt;=11,"Avenirs",IF((YEAR(F122)-D122)&lt;=13,"Benjamins",IF((YEAR(F122)-D122)&lt;=18,"Juniors",IF((YEAR(F122)-D122)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F122)-D122-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C123" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="D123" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E123" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G123" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="H123" s="1" t="str">
+        <f aca="false">IF((YEAR(F123)-D123)&lt;=11,"Avenirs",IF((YEAR(F123)-D123)&lt;=13,"Benjamins",IF((YEAR(F123)-D123)&lt;=18,"Juniors",IF((YEAR(F123)-D123)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F123)-D123-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C124" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="D124" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E124" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G124" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" s="1" t="str">
+        <f aca="false">IF((YEAR(F124)-D124)&lt;=11,"Avenirs",IF((YEAR(F124)-D124)&lt;=13,"Benjamins",IF((YEAR(F124)-D124)&lt;=18,"Juniors",IF((YEAR(F124)-D124)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F124)-D124-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C125" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="D125" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E125" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G125" s="0" t="n">
+        <v>184</v>
+      </c>
+      <c r="H125" s="1" t="str">
+        <f aca="false">IF((YEAR(F125)-D125)&lt;=11,"Avenirs",IF((YEAR(F125)-D125)&lt;=13,"Benjamins",IF((YEAR(F125)-D125)&lt;=18,"Juniors",IF((YEAR(F125)-D125)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F125)-D125-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C126" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="D126" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E126" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G126" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="H126" s="1" t="str">
+        <f aca="false">IF((YEAR(F126)-D126)&lt;=11,"Avenirs",IF((YEAR(F126)-D126)&lt;=13,"Benjamins",IF((YEAR(F126)-D126)&lt;=18,"Juniors",IF((YEAR(F126)-D126)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F126)-D126-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C127" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="D127" s="0" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E127" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G127" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="H127" s="1" t="str">
+        <f aca="false">IF((YEAR(F127)-D127)&lt;=11,"Avenirs",IF((YEAR(F127)-D127)&lt;=13,"Benjamins",IF((YEAR(F127)-D127)&lt;=18,"Juniors",IF((YEAR(F127)-D127)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F127)-D127-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C128" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="D128" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E128" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G128" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="H128" s="1" t="str">
+        <f aca="false">IF((YEAR(F128)-D128)&lt;=11,"Avenirs",IF((YEAR(F128)-D128)&lt;=13,"Benjamins",IF((YEAR(F128)-D128)&lt;=18,"Juniors",IF((YEAR(F128)-D128)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F128)-D128-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C129" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="D129" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E129" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G129" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="H129" s="1" t="str">
+        <f aca="false">IF((YEAR(F129)-D129)&lt;=11,"Avenirs",IF((YEAR(F129)-D129)&lt;=13,"Benjamins",IF((YEAR(F129)-D129)&lt;=18,"Juniors",IF((YEAR(F129)-D129)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F129)-D129-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B130" s="1"/>
+    </row>
+    <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B131" s="1"/>
     </row>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3964,19 +4453,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/data/resultats_xlsx.xlsx
+++ b/data/resultats_xlsx.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="225">
   <si>
     <t xml:space="preserve">EPREUVE</t>
   </si>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">Feminin</t>
   </si>
   <si>
-    <t xml:space="preserve">COSSART Zélie</t>
+    <t xml:space="preserve">COSSART Zelie</t>
   </si>
   <si>
     <t xml:space="preserve">00:32.75</t>
@@ -630,6 +630,60 @@
   </si>
   <si>
     <t xml:space="preserve">01:02.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:34.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:38.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERMEERSCH Anele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:38.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:41.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:42.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:38.69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:45.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:45.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 4 Nages Dames</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:38.48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:45.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:46.76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:50.55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:35.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 4 Nages Messieurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:43.65</t>
   </si>
   <si>
     <t xml:space="preserve">NOM_PRENOM</t>
@@ -3986,25 +4040,25 @@
       </c>
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0" t="s">
+      <c r="A114" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C114" s="0" t="s">
+      <c r="C114" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D114" s="0" t="n">
+      <c r="D114" s="1" t="n">
         <v>2016</v>
       </c>
-      <c r="E114" s="0" t="s">
+      <c r="E114" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="F114" s="4" t="s">
+      <c r="F114" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G114" s="0" t="n">
+      <c r="G114" s="1" t="n">
         <v>169</v>
       </c>
       <c r="H114" s="1" t="str">
@@ -4013,25 +4067,25 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="s">
+      <c r="A115" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C115" s="0" t="s">
+      <c r="C115" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D115" s="0" t="n">
+      <c r="D115" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E115" s="0" t="s">
+      <c r="E115" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F115" s="4" t="s">
+      <c r="F115" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G115" s="0" t="n">
+      <c r="G115" s="1" t="n">
         <v>3</v>
       </c>
       <c r="H115" s="1" t="str">
@@ -4040,25 +4094,25 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="0" t="s">
+      <c r="A116" s="1" t="s">
         <v>132</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C116" s="0" t="s">
+      <c r="C116" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D116" s="0" t="n">
+      <c r="D116" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E116" s="0" t="s">
+      <c r="E116" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F116" s="4" t="s">
+      <c r="F116" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G116" s="0" t="n">
+      <c r="G116" s="1" t="n">
         <v>141</v>
       </c>
       <c r="H116" s="1" t="str">
@@ -4067,25 +4121,25 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="0" t="s">
+      <c r="A117" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C117" s="0" t="s">
+      <c r="C117" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D117" s="0" t="n">
+      <c r="D117" s="1" t="n">
         <v>2016</v>
       </c>
-      <c r="E117" s="0" t="s">
+      <c r="E117" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F117" s="4" t="s">
+      <c r="F117" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G117" s="0" t="n">
+      <c r="G117" s="1" t="n">
         <v>123</v>
       </c>
       <c r="H117" s="1" t="str">
@@ -4094,25 +4148,25 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="s">
+      <c r="A118" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C118" s="0" t="s">
+      <c r="C118" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D118" s="0" t="n">
+      <c r="D118" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E118" s="0" t="s">
+      <c r="E118" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="F118" s="4" t="s">
+      <c r="F118" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G118" s="0" t="n">
+      <c r="G118" s="1" t="n">
         <v>93</v>
       </c>
       <c r="H118" s="1" t="str">
@@ -4121,25 +4175,25 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="0" t="s">
+      <c r="A119" s="1" t="s">
         <v>192</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C119" s="0" t="s">
+      <c r="C119" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D119" s="0" t="n">
+      <c r="D119" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E119" s="0" t="s">
+      <c r="E119" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F119" s="4" t="s">
+      <c r="F119" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G119" s="0" t="n">
+      <c r="G119" s="1" t="n">
         <v>299</v>
       </c>
       <c r="H119" s="1" t="str">
@@ -4148,25 +4202,25 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0" t="s">
+      <c r="A120" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C120" s="0" t="s">
+      <c r="C120" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D120" s="0" t="n">
+      <c r="D120" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E120" s="0" t="s">
+      <c r="E120" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F120" s="4" t="s">
+      <c r="F120" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G120" s="0" t="n">
+      <c r="G120" s="1" t="n">
         <v>246</v>
       </c>
       <c r="H120" s="1" t="str">
@@ -4175,25 +4229,25 @@
       </c>
     </row>
     <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0" t="s">
+      <c r="A121" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C121" s="0" t="s">
+      <c r="C121" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D121" s="0" t="n">
+      <c r="D121" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E121" s="0" t="s">
+      <c r="E121" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="F121" s="4" t="s">
+      <c r="F121" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G121" s="0" t="n">
+      <c r="G121" s="1" t="n">
         <v>121</v>
       </c>
       <c r="H121" s="1" t="str">
@@ -4202,25 +4256,25 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0" t="s">
+      <c r="A122" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C122" s="0" t="s">
+      <c r="C122" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D122" s="0" t="n">
+      <c r="D122" s="1" t="n">
         <v>2016</v>
       </c>
-      <c r="E122" s="0" t="s">
+      <c r="E122" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="F122" s="4" t="s">
+      <c r="F122" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G122" s="0" t="n">
+      <c r="G122" s="1" t="n">
         <v>52</v>
       </c>
       <c r="H122" s="1" t="str">
@@ -4229,25 +4283,25 @@
       </c>
     </row>
     <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="0" t="s">
+      <c r="A123" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C123" s="0" t="s">
+      <c r="C123" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D123" s="0" t="n">
+      <c r="D123" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E123" s="0" t="s">
+      <c r="E123" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F123" s="4" t="s">
+      <c r="F123" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G123" s="0" t="n">
+      <c r="G123" s="1" t="n">
         <v>39</v>
       </c>
       <c r="H123" s="1" t="str">
@@ -4256,25 +4310,25 @@
       </c>
     </row>
     <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="0" t="s">
+      <c r="A124" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C124" s="0" t="s">
+      <c r="C124" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D124" s="0" t="n">
+      <c r="D124" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E124" s="0" t="s">
+      <c r="E124" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F124" s="4" t="s">
+      <c r="F124" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G124" s="0" t="n">
+      <c r="G124" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H124" s="1" t="str">
@@ -4283,25 +4337,25 @@
       </c>
     </row>
     <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0" t="s">
+      <c r="A125" s="1" t="s">
         <v>151</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C125" s="0" t="s">
+      <c r="C125" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D125" s="0" t="n">
+      <c r="D125" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E125" s="0" t="s">
+      <c r="E125" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="F125" s="4" t="s">
+      <c r="F125" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G125" s="0" t="n">
+      <c r="G125" s="1" t="n">
         <v>184</v>
       </c>
       <c r="H125" s="1" t="str">
@@ -4310,25 +4364,25 @@
       </c>
     </row>
     <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="0" t="s">
+      <c r="A126" s="1" t="s">
         <v>151</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C126" s="0" t="s">
+      <c r="C126" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D126" s="0" t="n">
+      <c r="D126" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E126" s="0" t="s">
+      <c r="E126" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="F126" s="4" t="s">
+      <c r="F126" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G126" s="0" t="n">
+      <c r="G126" s="1" t="n">
         <v>63</v>
       </c>
       <c r="H126" s="1" t="str">
@@ -4337,25 +4391,25 @@
       </c>
     </row>
     <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="0" t="s">
+      <c r="A127" s="1" t="s">
         <v>151</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C127" s="0" t="s">
+      <c r="C127" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D127" s="0" t="n">
+      <c r="D127" s="1" t="n">
         <v>2016</v>
       </c>
-      <c r="E127" s="0" t="s">
+      <c r="E127" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F127" s="4" t="s">
+      <c r="F127" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G127" s="0" t="n">
+      <c r="G127" s="1" t="n">
         <v>54</v>
       </c>
       <c r="H127" s="1" t="str">
@@ -4364,25 +4418,25 @@
       </c>
     </row>
     <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="0" t="s">
+      <c r="A128" s="1" t="s">
         <v>151</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C128" s="0" t="s">
+      <c r="C128" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D128" s="0" t="n">
+      <c r="D128" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E128" s="0" t="s">
+      <c r="E128" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F128" s="4" t="s">
+      <c r="F128" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G128" s="0" t="n">
+      <c r="G128" s="1" t="n">
         <v>16</v>
       </c>
       <c r="H128" s="1" t="str">
@@ -4391,25 +4445,25 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="0" t="s">
+      <c r="A129" s="1" t="s">
         <v>151</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C129" s="0" t="s">
+      <c r="C129" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D129" s="0" t="n">
+      <c r="D129" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E129" s="0" t="s">
+      <c r="E129" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="F129" s="4" t="s">
+      <c r="F129" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G129" s="0" t="n">
+      <c r="G129" s="1" t="n">
         <v>12</v>
       </c>
       <c r="H129" s="1" t="str">
@@ -4418,10 +4472,382 @@
       </c>
     </row>
     <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B130" s="1"/>
+      <c r="A130" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C130" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="D130" s="0" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E130" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G130" s="0" t="n">
+        <v>691</v>
+      </c>
+      <c r="H130" s="1" t="str">
+        <f aca="false">IF((YEAR(F130)-D130)&lt;=11,"Avenirs",IF((YEAR(F130)-D130)&lt;=13,"Benjamins",IF((YEAR(F130)-D130)&lt;=18,"Juniors",IF((YEAR(F130)-D130)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F130)-D130-25)/5,0)))))</f>
+        <v>Benjamins</v>
+      </c>
     </row>
     <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B131" s="1"/>
+      <c r="A131" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C131" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" s="0" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E131" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G131" s="0" t="n">
+        <v>498</v>
+      </c>
+      <c r="H131" s="1" t="str">
+        <f aca="false">IF((YEAR(F131)-D131)&lt;=11,"Avenirs",IF((YEAR(F131)-D131)&lt;=13,"Benjamins",IF((YEAR(F131)-D131)&lt;=18,"Juniors",IF((YEAR(F131)-D131)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F131)-D131-25)/5,0)))))</f>
+        <v>Benjamins</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C132" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="D132" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E132" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G132" s="0" t="n">
+        <v>493</v>
+      </c>
+      <c r="H132" s="1" t="str">
+        <f aca="false">IF((YEAR(F132)-D132)&lt;=11,"Avenirs",IF((YEAR(F132)-D132)&lt;=13,"Benjamins",IF((YEAR(F132)-D132)&lt;=18,"Juniors",IF((YEAR(F132)-D132)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F132)-D132-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C133" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="D133" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E133" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G133" s="0" t="n">
+        <v>360</v>
+      </c>
+      <c r="H133" s="1" t="str">
+        <f aca="false">IF((YEAR(F133)-D133)&lt;=11,"Avenirs",IF((YEAR(F133)-D133)&lt;=13,"Benjamins",IF((YEAR(F133)-D133)&lt;=18,"Juniors",IF((YEAR(F133)-D133)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F133)-D133-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C134" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="D134" s="0" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E134" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G134" s="0" t="n">
+        <v>325</v>
+      </c>
+      <c r="H134" s="1" t="str">
+        <f aca="false">IF((YEAR(F134)-D134)&lt;=11,"Avenirs",IF((YEAR(F134)-D134)&lt;=13,"Benjamins",IF((YEAR(F134)-D134)&lt;=18,"Juniors",IF((YEAR(F134)-D134)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F134)-D134-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C135" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="D135" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E135" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G135" s="0" t="n">
+        <v>647</v>
+      </c>
+      <c r="H135" s="1" t="str">
+        <f aca="false">IF((YEAR(F135)-D135)&lt;=11,"Avenirs",IF((YEAR(F135)-D135)&lt;=13,"Benjamins",IF((YEAR(F135)-D135)&lt;=18,"Juniors",IF((YEAR(F135)-D135)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F135)-D135-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C136" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="D136" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E136" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G136" s="0" t="n">
+        <v>539</v>
+      </c>
+      <c r="H136" s="1" t="str">
+        <f aca="false">IF((YEAR(F136)-D136)&lt;=11,"Avenirs",IF((YEAR(F136)-D136)&lt;=13,"Benjamins",IF((YEAR(F136)-D136)&lt;=18,"Juniors",IF((YEAR(F136)-D136)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F136)-D136-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C137" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" s="0" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E137" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G137" s="0" t="n">
+        <v>528</v>
+      </c>
+      <c r="H137" s="1" t="str">
+        <f aca="false">IF((YEAR(F137)-D137)&lt;=11,"Avenirs",IF((YEAR(F137)-D137)&lt;=13,"Benjamins",IF((YEAR(F137)-D137)&lt;=18,"Juniors",IF((YEAR(F137)-D137)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F137)-D137-25)/5,0)))))</f>
+        <v>Benjamins</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C138" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="D138" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E138" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G138" s="0" t="n">
+        <v>431</v>
+      </c>
+      <c r="H138" s="1" t="str">
+        <f aca="false">IF((YEAR(F138)-D138)&lt;=11,"Avenirs",IF((YEAR(F138)-D138)&lt;=13,"Benjamins",IF((YEAR(F138)-D138)&lt;=18,"Juniors",IF((YEAR(F138)-D138)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F138)-D138-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C139" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="D139" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E139" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G139" s="0" t="n">
+        <v>319</v>
+      </c>
+      <c r="H139" s="1" t="str">
+        <f aca="false">IF((YEAR(F139)-D139)&lt;=11,"Avenirs",IF((YEAR(F139)-D139)&lt;=13,"Benjamins",IF((YEAR(F139)-D139)&lt;=18,"Juniors",IF((YEAR(F139)-D139)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F139)-D139-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C140" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="D140" s="0" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E140" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G140" s="0" t="n">
+        <v>299</v>
+      </c>
+      <c r="H140" s="1" t="str">
+        <f aca="false">IF((YEAR(F140)-D140)&lt;=11,"Avenirs",IF((YEAR(F140)-D140)&lt;=13,"Benjamins",IF((YEAR(F140)-D140)&lt;=18,"Juniors",IF((YEAR(F140)-D140)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F140)-D140-25)/5,0)))))</f>
+        <v>Benjamins</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C141" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="D141" s="0" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E141" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G141" s="0" t="n">
+        <v>247</v>
+      </c>
+      <c r="H141" s="1" t="str">
+        <f aca="false">IF((YEAR(F141)-D141)&lt;=11,"Avenirs",IF((YEAR(F141)-D141)&lt;=13,"Benjamins",IF((YEAR(F141)-D141)&lt;=18,"Juniors",IF((YEAR(F141)-D141)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F141)-D141-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="D142" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E142" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G142" s="0" t="n">
+        <v>516</v>
+      </c>
+      <c r="H142" s="1" t="str">
+        <f aca="false">IF((YEAR(F142)-D142)&lt;=11,"Avenirs",IF((YEAR(F142)-D142)&lt;=13,"Benjamins",IF((YEAR(F142)-D142)&lt;=18,"Juniors",IF((YEAR(F142)-D142)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F142)-D142-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C143" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="D143" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E143" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G143" s="0" t="n">
+        <v>207</v>
+      </c>
+      <c r="H143" s="1" t="str">
+        <f aca="false">IF((YEAR(F143)-D143)&lt;=11,"Avenirs",IF((YEAR(F143)-D143)&lt;=13,"Benjamins",IF((YEAR(F143)-D143)&lt;=18,"Juniors",IF((YEAR(F143)-D143)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F143)-D143-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
     </row>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -4453,19 +4879,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/data/resultats_xlsx.xlsx
+++ b/data/resultats_xlsx.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="259">
   <si>
     <t xml:space="preserve">EPREUVE</t>
   </si>
@@ -684,6 +684,108 @@
   </si>
   <si>
     <t xml:space="preserve">01:43.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:35.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:37.81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:38.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:40.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:42.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:43.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:44.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:45.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:57.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:42.57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:52.87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:46.54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:49.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:50.58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:54.34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:55.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:05.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:46.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:49.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:30.57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:36.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERROUST Sacha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:37.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:47.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:52.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:37.59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:43.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:49.82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:53.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 Brasse Messieurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:50.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:15.57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:39.40</t>
   </si>
   <si>
     <t xml:space="preserve">NOM_PRENOM</t>
@@ -4472,25 +4574,25 @@
       </c>
     </row>
     <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="0" t="s">
+      <c r="A130" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C130" s="0" t="s">
+      <c r="C130" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D130" s="0" t="n">
+      <c r="D130" s="1" t="n">
         <v>2013</v>
       </c>
-      <c r="E130" s="0" t="s">
+      <c r="E130" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F130" s="4" t="s">
+      <c r="F130" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G130" s="0" t="n">
+      <c r="G130" s="1" t="n">
         <v>691</v>
       </c>
       <c r="H130" s="1" t="str">
@@ -4499,25 +4601,25 @@
       </c>
     </row>
     <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="0" t="s">
+      <c r="A131" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C131" s="0" t="s">
+      <c r="C131" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D131" s="0" t="n">
+      <c r="D131" s="1" t="n">
         <v>2013</v>
       </c>
-      <c r="E131" s="0" t="s">
+      <c r="E131" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F131" s="4" t="s">
+      <c r="F131" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G131" s="0" t="n">
+      <c r="G131" s="1" t="n">
         <v>498</v>
       </c>
       <c r="H131" s="1" t="str">
@@ -4526,25 +4628,25 @@
       </c>
     </row>
     <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="0" t="s">
+      <c r="A132" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C132" s="0" t="s">
+      <c r="C132" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D132" s="0" t="n">
+      <c r="D132" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E132" s="0" t="s">
+      <c r="E132" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="F132" s="4" t="s">
+      <c r="F132" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G132" s="0" t="n">
+      <c r="G132" s="1" t="n">
         <v>493</v>
       </c>
       <c r="H132" s="1" t="str">
@@ -4553,25 +4655,25 @@
       </c>
     </row>
     <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="0" t="s">
+      <c r="A133" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C133" s="0" t="s">
+      <c r="C133" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D133" s="0" t="n">
+      <c r="D133" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E133" s="0" t="s">
+      <c r="E133" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F133" s="4" t="s">
+      <c r="F133" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G133" s="0" t="n">
+      <c r="G133" s="1" t="n">
         <v>360</v>
       </c>
       <c r="H133" s="1" t="str">
@@ -4580,25 +4682,25 @@
       </c>
     </row>
     <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="0" t="s">
+      <c r="A134" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C134" s="0" t="s">
+      <c r="C134" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D134" s="0" t="n">
+      <c r="D134" s="1" t="n">
         <v>2010</v>
       </c>
-      <c r="E134" s="0" t="s">
+      <c r="E134" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F134" s="4" t="s">
+      <c r="F134" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G134" s="0" t="n">
+      <c r="G134" s="1" t="n">
         <v>325</v>
       </c>
       <c r="H134" s="1" t="str">
@@ -4607,25 +4709,25 @@
       </c>
     </row>
     <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="0" t="s">
+      <c r="A135" s="1" t="s">
         <v>192</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C135" s="0" t="s">
+      <c r="C135" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D135" s="0" t="n">
+      <c r="D135" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E135" s="0" t="s">
+      <c r="E135" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F135" s="4" t="s">
+      <c r="F135" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G135" s="0" t="n">
+      <c r="G135" s="1" t="n">
         <v>647</v>
       </c>
       <c r="H135" s="1" t="str">
@@ -4634,25 +4736,25 @@
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="0" t="s">
+      <c r="A136" s="1" t="s">
         <v>192</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C136" s="0" t="s">
+      <c r="C136" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D136" s="0" t="n">
+      <c r="D136" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E136" s="0" t="s">
+      <c r="E136" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="F136" s="4" t="s">
+      <c r="F136" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G136" s="0" t="n">
+      <c r="G136" s="1" t="n">
         <v>539</v>
       </c>
       <c r="H136" s="1" t="str">
@@ -4661,25 +4763,25 @@
       </c>
     </row>
     <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="0" t="s">
+      <c r="A137" s="1" t="s">
         <v>192</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C137" s="0" t="s">
+      <c r="C137" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D137" s="0" t="n">
+      <c r="D137" s="1" t="n">
         <v>2013</v>
       </c>
-      <c r="E137" s="0" t="s">
+      <c r="E137" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F137" s="4" t="s">
+      <c r="F137" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G137" s="0" t="n">
+      <c r="G137" s="1" t="n">
         <v>528</v>
       </c>
       <c r="H137" s="1" t="str">
@@ -4688,25 +4790,25 @@
       </c>
     </row>
     <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="0" t="s">
+      <c r="A138" s="1" t="s">
         <v>213</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C138" s="0" t="s">
+      <c r="C138" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D138" s="0" t="n">
+      <c r="D138" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E138" s="0" t="s">
+      <c r="E138" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F138" s="4" t="s">
+      <c r="F138" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G138" s="0" t="n">
+      <c r="G138" s="1" t="n">
         <v>431</v>
       </c>
       <c r="H138" s="1" t="str">
@@ -4715,25 +4817,25 @@
       </c>
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="0" t="s">
+      <c r="A139" s="1" t="s">
         <v>213</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C139" s="0" t="s">
+      <c r="C139" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D139" s="0" t="n">
+      <c r="D139" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E139" s="0" t="s">
+      <c r="E139" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F139" s="4" t="s">
+      <c r="F139" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G139" s="0" t="n">
+      <c r="G139" s="1" t="n">
         <v>319</v>
       </c>
       <c r="H139" s="1" t="str">
@@ -4742,25 +4844,25 @@
       </c>
     </row>
     <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="0" t="s">
+      <c r="A140" s="1" t="s">
         <v>213</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C140" s="0" t="s">
+      <c r="C140" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D140" s="0" t="n">
+      <c r="D140" s="1" t="n">
         <v>2013</v>
       </c>
-      <c r="E140" s="0" t="s">
+      <c r="E140" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F140" s="4" t="s">
+      <c r="F140" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G140" s="0" t="n">
+      <c r="G140" s="1" t="n">
         <v>299</v>
       </c>
       <c r="H140" s="1" t="str">
@@ -4769,25 +4871,25 @@
       </c>
     </row>
     <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="0" t="s">
+      <c r="A141" s="1" t="s">
         <v>213</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C141" s="0" t="s">
+      <c r="C141" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D141" s="0" t="n">
+      <c r="D141" s="1" t="n">
         <v>2010</v>
       </c>
-      <c r="E141" s="0" t="s">
+      <c r="E141" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F141" s="4" t="s">
+      <c r="F141" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G141" s="0" t="n">
+      <c r="G141" s="1" t="n">
         <v>247</v>
       </c>
       <c r="H141" s="1" t="str">
@@ -4796,25 +4898,25 @@
       </c>
     </row>
     <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="0" t="s">
+      <c r="A142" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C142" s="0" t="s">
+      <c r="C142" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D142" s="0" t="n">
+      <c r="D142" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E142" s="0" t="s">
+      <c r="E142" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F142" s="4" t="s">
+      <c r="F142" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G142" s="0" t="n">
+      <c r="G142" s="1" t="n">
         <v>516</v>
       </c>
       <c r="H142" s="1" t="str">
@@ -4823,31 +4925,904 @@
       </c>
     </row>
     <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="0" t="s">
+      <c r="A143" s="1" t="s">
         <v>219</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C143" s="0" t="s">
+      <c r="C143" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D143" s="0" t="n">
+      <c r="D143" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E143" s="0" t="s">
+      <c r="E143" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="F143" s="4" t="s">
+      <c r="F143" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G143" s="0" t="n">
+      <c r="G143" s="1" t="n">
         <v>207</v>
       </c>
       <c r="H143" s="1" t="str">
         <f aca="false">IF((YEAR(F143)-D143)&lt;=11,"Avenirs",IF((YEAR(F143)-D143)&lt;=13,"Benjamins",IF((YEAR(F143)-D143)&lt;=18,"Juniors",IF((YEAR(F143)-D143)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F143)-D143-25)/5,0)))))</f>
         <v>Juniors</v>
       </c>
+    </row>
+    <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C144" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="D144" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E144" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G144" s="0" t="n">
+        <v>652</v>
+      </c>
+      <c r="H144" s="1" t="str">
+        <f aca="false">IF((YEAR(F144)-D144)&lt;=11,"Avenirs",IF((YEAR(F144)-D144)&lt;=13,"Benjamins",IF((YEAR(F144)-D144)&lt;=18,"Juniors",IF((YEAR(F144)-D144)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F144)-D144-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C145" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="D145" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E145" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G145" s="0" t="n">
+        <v>511</v>
+      </c>
+      <c r="H145" s="1" t="str">
+        <f aca="false">IF((YEAR(F145)-D145)&lt;=11,"Avenirs",IF((YEAR(F145)-D145)&lt;=13,"Benjamins",IF((YEAR(F145)-D145)&lt;=18,"Juniors",IF((YEAR(F145)-D145)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F145)-D145-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C146" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="D146" s="0" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E146" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G146" s="0" t="n">
+        <v>497</v>
+      </c>
+      <c r="H146" s="1" t="str">
+        <f aca="false">IF((YEAR(F146)-D146)&lt;=11,"Avenirs",IF((YEAR(F146)-D146)&lt;=13,"Benjamins",IF((YEAR(F146)-D146)&lt;=18,"Juniors",IF((YEAR(F146)-D146)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F146)-D146-25)/5,0)))))</f>
+        <v>Benjamins</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C147" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="D147" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E147" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G147" s="0" t="n">
+        <v>377</v>
+      </c>
+      <c r="H147" s="1" t="str">
+        <f aca="false">IF((YEAR(F147)-D147)&lt;=11,"Avenirs",IF((YEAR(F147)-D147)&lt;=13,"Benjamins",IF((YEAR(F147)-D147)&lt;=18,"Juniors",IF((YEAR(F147)-D147)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F147)-D147-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C148" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="D148" s="0" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E148" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G148" s="0" t="n">
+        <v>321</v>
+      </c>
+      <c r="H148" s="1" t="str">
+        <f aca="false">IF((YEAR(F148)-D148)&lt;=11,"Avenirs",IF((YEAR(F148)-D148)&lt;=13,"Benjamins",IF((YEAR(F148)-D148)&lt;=18,"Juniors",IF((YEAR(F148)-D148)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F148)-D148-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C149" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="D149" s="0" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E149" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G149" s="0" t="n">
+        <v>278</v>
+      </c>
+      <c r="H149" s="1" t="str">
+        <f aca="false">IF((YEAR(F149)-D149)&lt;=11,"Avenirs",IF((YEAR(F149)-D149)&lt;=13,"Benjamins",IF((YEAR(F149)-D149)&lt;=18,"Juniors",IF((YEAR(F149)-D149)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F149)-D149-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C150" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="D150" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E150" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G150" s="0" t="n">
+        <v>244</v>
+      </c>
+      <c r="H150" s="1" t="str">
+        <f aca="false">IF((YEAR(F150)-D150)&lt;=11,"Avenirs",IF((YEAR(F150)-D150)&lt;=13,"Benjamins",IF((YEAR(F150)-D150)&lt;=18,"Juniors",IF((YEAR(F150)-D150)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F150)-D150-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C151" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="D151" s="0" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E151" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G151" s="0" t="n">
+        <v>218</v>
+      </c>
+      <c r="H151" s="1" t="str">
+        <f aca="false">IF((YEAR(F151)-D151)&lt;=11,"Avenirs",IF((YEAR(F151)-D151)&lt;=13,"Benjamins",IF((YEAR(F151)-D151)&lt;=18,"Juniors",IF((YEAR(F151)-D151)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F151)-D151-25)/5,0)))))</f>
+        <v>Benjamins</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C152" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="D152" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E152" s="0" t="s">
+        <v>230</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G152" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="H152" s="1" t="str">
+        <f aca="false">IF((YEAR(F152)-D152)&lt;=11,"Avenirs",IF((YEAR(F152)-D152)&lt;=13,"Benjamins",IF((YEAR(F152)-D152)&lt;=18,"Juniors",IF((YEAR(F152)-D152)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F152)-D152-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C153" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="D153" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E153" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G153" s="0" t="n">
+        <v>583</v>
+      </c>
+      <c r="H153" s="1" t="str">
+        <f aca="false">IF((YEAR(F153)-D153)&lt;=11,"Avenirs",IF((YEAR(F153)-D153)&lt;=13,"Benjamins",IF((YEAR(F153)-D153)&lt;=18,"Juniors",IF((YEAR(F153)-D153)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F153)-D153-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C154" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="D154" s="0" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E154" s="0" t="s">
+        <v>232</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G154" s="0" t="n">
+        <v>246</v>
+      </c>
+      <c r="H154" s="1" t="str">
+        <f aca="false">IF((YEAR(F154)-D154)&lt;=11,"Avenirs",IF((YEAR(F154)-D154)&lt;=13,"Benjamins",IF((YEAR(F154)-D154)&lt;=18,"Juniors",IF((YEAR(F154)-D154)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F154)-D154-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C155" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="D155" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E155" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G155" s="0" t="n">
+        <v>575</v>
+      </c>
+      <c r="H155" s="1" t="str">
+        <f aca="false">IF((YEAR(F155)-D155)&lt;=11,"Avenirs",IF((YEAR(F155)-D155)&lt;=13,"Benjamins",IF((YEAR(F155)-D155)&lt;=18,"Juniors",IF((YEAR(F155)-D155)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F155)-D155-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C156" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="D156" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E156" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G156" s="0" t="n">
+        <v>456</v>
+      </c>
+      <c r="H156" s="1" t="str">
+        <f aca="false">IF((YEAR(F156)-D156)&lt;=11,"Avenirs",IF((YEAR(F156)-D156)&lt;=13,"Benjamins",IF((YEAR(F156)-D156)&lt;=18,"Juniors",IF((YEAR(F156)-D156)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F156)-D156-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C157" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" s="0" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E157" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G157" s="0" t="n">
+        <v>432</v>
+      </c>
+      <c r="H157" s="1" t="str">
+        <f aca="false">IF((YEAR(F157)-D157)&lt;=11,"Avenirs",IF((YEAR(F157)-D157)&lt;=13,"Benjamins",IF((YEAR(F157)-D157)&lt;=18,"Juniors",IF((YEAR(F157)-D157)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F157)-D157-25)/5,0)))))</f>
+        <v>Benjamins</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C158" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="D158" s="0" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E158" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G158" s="0" t="n">
+        <v>317</v>
+      </c>
+      <c r="H158" s="1" t="str">
+        <f aca="false">IF((YEAR(F158)-D158)&lt;=11,"Avenirs",IF((YEAR(F158)-D158)&lt;=13,"Benjamins",IF((YEAR(F158)-D158)&lt;=18,"Juniors",IF((YEAR(F158)-D158)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F158)-D158-25)/5,0)))))</f>
+        <v>Benjamins</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C159" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="D159" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E159" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G159" s="0" t="n">
+        <v>298</v>
+      </c>
+      <c r="H159" s="1" t="str">
+        <f aca="false">IF((YEAR(F159)-D159)&lt;=11,"Avenirs",IF((YEAR(F159)-D159)&lt;=13,"Benjamins",IF((YEAR(F159)-D159)&lt;=18,"Juniors",IF((YEAR(F159)-D159)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F159)-D159-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C160" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="D160" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E160" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G160" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="H160" s="1" t="str">
+        <f aca="false">IF((YEAR(F160)-D160)&lt;=11,"Avenirs",IF((YEAR(F160)-D160)&lt;=13,"Benjamins",IF((YEAR(F160)-D160)&lt;=18,"Juniors",IF((YEAR(F160)-D160)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F160)-D160-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C161" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="D161" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E161" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G161" s="0" t="n">
+        <v>312</v>
+      </c>
+      <c r="H161" s="1" t="str">
+        <f aca="false">IF((YEAR(F161)-D161)&lt;=11,"Avenirs",IF((YEAR(F161)-D161)&lt;=13,"Benjamins",IF((YEAR(F161)-D161)&lt;=18,"Juniors",IF((YEAR(F161)-D161)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F161)-D161-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C162" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="D162" s="0" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E162" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G162" s="0" t="n">
+        <v>208</v>
+      </c>
+      <c r="H162" s="1" t="str">
+        <f aca="false">IF((YEAR(F162)-D162)&lt;=11,"Avenirs",IF((YEAR(F162)-D162)&lt;=13,"Benjamins",IF((YEAR(F162)-D162)&lt;=18,"Juniors",IF((YEAR(F162)-D162)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F162)-D162-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C163" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="D163" s="0" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E163" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G163" s="0" t="n">
+        <v>752</v>
+      </c>
+      <c r="H163" s="1" t="str">
+        <f aca="false">IF((YEAR(F163)-D163)&lt;=11,"Avenirs",IF((YEAR(F163)-D163)&lt;=13,"Benjamins",IF((YEAR(F163)-D163)&lt;=18,"Juniors",IF((YEAR(F163)-D163)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F163)-D163-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C164" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="D164" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E164" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G164" s="0" t="n">
+        <v>463</v>
+      </c>
+      <c r="H164" s="1" t="str">
+        <f aca="false">IF((YEAR(F164)-D164)&lt;=11,"Avenirs",IF((YEAR(F164)-D164)&lt;=13,"Benjamins",IF((YEAR(F164)-D164)&lt;=18,"Juniors",IF((YEAR(F164)-D164)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F164)-D164-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C165" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="D165" s="0" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E165" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="F165" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G165" s="0" t="n">
+        <v>403</v>
+      </c>
+      <c r="H165" s="1" t="str">
+        <f aca="false">IF((YEAR(F165)-D165)&lt;=11,"Avenirs",IF((YEAR(F165)-D165)&lt;=13,"Benjamins",IF((YEAR(F165)-D165)&lt;=18,"Juniors",IF((YEAR(F165)-D165)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F165)-D165-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C166" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="D166" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E166" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="F166" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G166" s="0" t="n">
+        <v>263</v>
+      </c>
+      <c r="H166" s="1" t="str">
+        <f aca="false">IF((YEAR(F166)-D166)&lt;=11,"Avenirs",IF((YEAR(F166)-D166)&lt;=13,"Benjamins",IF((YEAR(F166)-D166)&lt;=18,"Juniors",IF((YEAR(F166)-D166)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F166)-D166-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C167" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="D167" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E167" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="F167" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G167" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="H167" s="1" t="str">
+        <f aca="false">IF((YEAR(F167)-D167)&lt;=11,"Avenirs",IF((YEAR(F167)-D167)&lt;=13,"Benjamins",IF((YEAR(F167)-D167)&lt;=18,"Juniors",IF((YEAR(F167)-D167)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F167)-D167-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C168" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="D168" s="0" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E168" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G168" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="H168" s="1" t="str">
+        <f aca="false">IF((YEAR(F168)-D168)&lt;=11,"Avenirs",IF((YEAR(F168)-D168)&lt;=13,"Benjamins",IF((YEAR(F168)-D168)&lt;=18,"Juniors",IF((YEAR(F168)-D168)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F168)-D168-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C169" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="D169" s="0" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E169" s="0" t="s">
+        <v>247</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G169" s="0" t="n">
+        <v>620</v>
+      </c>
+      <c r="H169" s="1" t="str">
+        <f aca="false">IF((YEAR(F169)-D169)&lt;=11,"Avenirs",IF((YEAR(F169)-D169)&lt;=13,"Benjamins",IF((YEAR(F169)-D169)&lt;=18,"Juniors",IF((YEAR(F169)-D169)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F169)-D169-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C170" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="D170" s="0" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E170" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G170" s="0" t="n">
+        <v>391</v>
+      </c>
+      <c r="H170" s="1" t="str">
+        <f aca="false">IF((YEAR(F170)-D170)&lt;=11,"Avenirs",IF((YEAR(F170)-D170)&lt;=13,"Benjamins",IF((YEAR(F170)-D170)&lt;=18,"Juniors",IF((YEAR(F170)-D170)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F170)-D170-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C171" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="D171" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E171" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G171" s="0" t="n">
+        <v>201</v>
+      </c>
+      <c r="H171" s="1" t="str">
+        <f aca="false">IF((YEAR(F171)-D171)&lt;=11,"Avenirs",IF((YEAR(F171)-D171)&lt;=13,"Benjamins",IF((YEAR(F171)-D171)&lt;=18,"Juniors",IF((YEAR(F171)-D171)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F171)-D171-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C172" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="D172" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E172" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G172" s="0" t="n">
+        <v>124</v>
+      </c>
+      <c r="H172" s="1" t="str">
+        <f aca="false">IF((YEAR(F172)-D172)&lt;=11,"Avenirs",IF((YEAR(F172)-D172)&lt;=13,"Benjamins",IF((YEAR(F172)-D172)&lt;=18,"Juniors",IF((YEAR(F172)-D172)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F172)-D172-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C173" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="D173" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E173" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G173" s="0" t="n">
+        <v>316</v>
+      </c>
+      <c r="H173" s="1" t="str">
+        <f aca="false">IF((YEAR(F173)-D173)&lt;=11,"Avenirs",IF((YEAR(F173)-D173)&lt;=13,"Benjamins",IF((YEAR(F173)-D173)&lt;=18,"Juniors",IF((YEAR(F173)-D173)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F173)-D173-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C174" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="D174" s="0" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E174" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G174" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" s="1" t="str">
+        <f aca="false">IF((YEAR(F174)-D174)&lt;=11,"Avenirs",IF((YEAR(F174)-D174)&lt;=13,"Benjamins",IF((YEAR(F174)-D174)&lt;=18,"Juniors",IF((YEAR(F174)-D174)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F174)-D174-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C175" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="D175" s="0" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E175" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G175" s="0" t="n">
+        <v>425</v>
+      </c>
+      <c r="H175" s="1" t="str">
+        <f aca="false">IF((YEAR(F175)-D175)&lt;=11,"Avenirs",IF((YEAR(F175)-D175)&lt;=13,"Benjamins",IF((YEAR(F175)-D175)&lt;=18,"Juniors",IF((YEAR(F175)-D175)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F175)-D175-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B176" s="1"/>
+    </row>
+    <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B177" s="1"/>
+    </row>
+    <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B178" s="1"/>
     </row>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -4879,19 +5854,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>221</v>
+        <v>255</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>223</v>
+        <v>257</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>224</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/data/resultats_xlsx.xlsx
+++ b/data/resultats_xlsx.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="258">
   <si>
     <t xml:space="preserve">EPREUVE</t>
   </si>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">200 Brasse Dames</t>
   </si>
   <si>
-    <t xml:space="preserve">VERMEERSCH Anèle</t>
+    <t xml:space="preserve">VERMEERSCH Anele</t>
   </si>
   <si>
     <t xml:space="preserve">03:44.56</t>
@@ -639,9 +639,6 @@
   </si>
   <si>
     <t xml:space="preserve">00:38.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERMEERSCH Anele</t>
   </si>
   <si>
     <t xml:space="preserve">00:38.18</t>
@@ -875,7 +872,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -889,10 +886,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4635,13 +4628,13 @@
         <v>47</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="D132" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>204</v>
@@ -4668,7 +4661,7 @@
         <v>2012</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>204</v>
@@ -4695,7 +4688,7 @@
         <v>2010</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>204</v>
@@ -4716,13 +4709,13 @@
         <v>47</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="D135" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>204</v>
@@ -4749,7 +4742,7 @@
         <v>2012</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>204</v>
@@ -4776,7 +4769,7 @@
         <v>2013</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>204</v>
@@ -4791,19 +4784,19 @@
     </row>
     <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="D138" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>204</v>
@@ -4818,7 +4811,7 @@
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>47</v>
@@ -4830,7 +4823,7 @@
         <v>2012</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>204</v>
@@ -4845,7 +4838,7 @@
     </row>
     <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>47</v>
@@ -4857,7 +4850,7 @@
         <v>2013</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>204</v>
@@ -4872,7 +4865,7 @@
     </row>
     <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>47</v>
@@ -4884,7 +4877,7 @@
         <v>2010</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>204</v>
@@ -4911,7 +4904,7 @@
         <v>2012</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>204</v>
@@ -4926,7 +4919,7 @@
     </row>
     <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>9</v>
@@ -4938,7 +4931,7 @@
         <v>2012</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>204</v>
@@ -4952,25 +4945,25 @@
       </c>
     </row>
     <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="0" t="s">
+      <c r="A144" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C144" s="0" t="s">
+      <c r="C144" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D144" s="0" t="n">
+      <c r="D144" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E144" s="0" t="s">
+      <c r="E144" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F144" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="F144" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G144" s="0" t="n">
+      <c r="G144" s="1" t="n">
         <v>652</v>
       </c>
       <c r="H144" s="1" t="str">
@@ -4979,25 +4972,25 @@
       </c>
     </row>
     <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="0" t="s">
+      <c r="A145" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C145" s="0" t="s">
-        <v>206</v>
-      </c>
-      <c r="D145" s="0" t="n">
+      <c r="C145" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D145" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E145" s="0" t="s">
-        <v>223</v>
-      </c>
-      <c r="F145" s="4" t="s">
+      <c r="E145" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="G145" s="0" t="n">
+      <c r="F145" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G145" s="1" t="n">
         <v>511</v>
       </c>
       <c r="H145" s="1" t="str">
@@ -5006,25 +4999,25 @@
       </c>
     </row>
     <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="0" t="s">
+      <c r="A146" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C146" s="0" t="s">
+      <c r="C146" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D146" s="0" t="n">
+      <c r="D146" s="1" t="n">
         <v>2013</v>
       </c>
-      <c r="E146" s="0" t="s">
-        <v>224</v>
-      </c>
-      <c r="F146" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G146" s="0" t="n">
+      <c r="E146" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G146" s="1" t="n">
         <v>497</v>
       </c>
       <c r="H146" s="1" t="str">
@@ -5033,25 +5026,25 @@
       </c>
     </row>
     <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="0" t="s">
+      <c r="A147" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C147" s="0" t="s">
+      <c r="C147" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D147" s="0" t="n">
+      <c r="D147" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E147" s="0" t="s">
-        <v>225</v>
-      </c>
-      <c r="F147" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G147" s="0" t="n">
+      <c r="E147" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G147" s="1" t="n">
         <v>377</v>
       </c>
       <c r="H147" s="1" t="str">
@@ -5060,25 +5053,25 @@
       </c>
     </row>
     <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="0" t="s">
+      <c r="A148" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C148" s="0" t="s">
+      <c r="C148" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D148" s="0" t="n">
+      <c r="D148" s="1" t="n">
         <v>2010</v>
       </c>
-      <c r="E148" s="0" t="s">
-        <v>226</v>
-      </c>
-      <c r="F148" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G148" s="0" t="n">
+      <c r="E148" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G148" s="1" t="n">
         <v>321</v>
       </c>
       <c r="H148" s="1" t="str">
@@ -5087,25 +5080,25 @@
       </c>
     </row>
     <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="0" t="s">
+      <c r="A149" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C149" s="0" t="s">
+      <c r="C149" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D149" s="0" t="n">
+      <c r="D149" s="1" t="n">
         <v>2016</v>
       </c>
-      <c r="E149" s="0" t="s">
-        <v>227</v>
-      </c>
-      <c r="F149" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G149" s="0" t="n">
+      <c r="E149" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G149" s="1" t="n">
         <v>278</v>
       </c>
       <c r="H149" s="1" t="str">
@@ -5114,25 +5107,25 @@
       </c>
     </row>
     <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="0" t="s">
+      <c r="A150" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C150" s="0" t="s">
+      <c r="C150" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D150" s="0" t="n">
+      <c r="D150" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E150" s="0" t="s">
-        <v>228</v>
-      </c>
-      <c r="F150" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G150" s="0" t="n">
+      <c r="E150" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G150" s="1" t="n">
         <v>244</v>
       </c>
       <c r="H150" s="1" t="str">
@@ -5141,25 +5134,25 @@
       </c>
     </row>
     <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="0" t="s">
+      <c r="A151" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C151" s="0" t="s">
+      <c r="C151" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D151" s="0" t="n">
+      <c r="D151" s="1" t="n">
         <v>2014</v>
       </c>
-      <c r="E151" s="0" t="s">
-        <v>229</v>
-      </c>
-      <c r="F151" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G151" s="0" t="n">
+      <c r="E151" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G151" s="1" t="n">
         <v>218</v>
       </c>
       <c r="H151" s="1" t="str">
@@ -5168,25 +5161,25 @@
       </c>
     </row>
     <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="0" t="s">
+      <c r="A152" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C152" s="0" t="s">
+      <c r="C152" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D152" s="0" t="n">
+      <c r="D152" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E152" s="0" t="s">
-        <v>230</v>
-      </c>
-      <c r="F152" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G152" s="0" t="n">
+      <c r="E152" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G152" s="1" t="n">
         <v>5</v>
       </c>
       <c r="H152" s="1" t="str">
@@ -5195,25 +5188,25 @@
       </c>
     </row>
     <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="0" t="s">
+      <c r="A153" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C153" s="0" t="s">
+      <c r="C153" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D153" s="0" t="n">
+      <c r="D153" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E153" s="0" t="s">
-        <v>231</v>
-      </c>
-      <c r="F153" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G153" s="0" t="n">
+      <c r="E153" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G153" s="1" t="n">
         <v>583</v>
       </c>
       <c r="H153" s="1" t="str">
@@ -5222,25 +5215,25 @@
       </c>
     </row>
     <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="0" t="s">
+      <c r="A154" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C154" s="0" t="s">
+      <c r="C154" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D154" s="0" t="n">
+      <c r="D154" s="1" t="n">
         <v>2016</v>
       </c>
-      <c r="E154" s="0" t="s">
-        <v>232</v>
-      </c>
-      <c r="F154" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G154" s="0" t="n">
+      <c r="E154" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G154" s="1" t="n">
         <v>246</v>
       </c>
       <c r="H154" s="1" t="str">
@@ -5249,25 +5242,25 @@
       </c>
     </row>
     <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="0" t="s">
+      <c r="A155" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C155" s="0" t="s">
-        <v>206</v>
-      </c>
-      <c r="D155" s="0" t="n">
+      <c r="C155" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D155" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E155" s="0" t="s">
-        <v>233</v>
-      </c>
-      <c r="F155" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G155" s="0" t="n">
+      <c r="E155" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G155" s="1" t="n">
         <v>575</v>
       </c>
       <c r="H155" s="1" t="str">
@@ -5276,25 +5269,25 @@
       </c>
     </row>
     <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="0" t="s">
+      <c r="A156" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C156" s="0" t="s">
+      <c r="C156" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D156" s="0" t="n">
+      <c r="D156" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E156" s="0" t="s">
-        <v>234</v>
-      </c>
-      <c r="F156" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G156" s="0" t="n">
+      <c r="E156" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G156" s="1" t="n">
         <v>456</v>
       </c>
       <c r="H156" s="1" t="str">
@@ -5303,25 +5296,25 @@
       </c>
     </row>
     <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="0" t="s">
+      <c r="A157" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C157" s="0" t="s">
+      <c r="C157" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D157" s="0" t="n">
+      <c r="D157" s="1" t="n">
         <v>2013</v>
       </c>
-      <c r="E157" s="0" t="s">
-        <v>235</v>
-      </c>
-      <c r="F157" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G157" s="0" t="n">
+      <c r="E157" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G157" s="1" t="n">
         <v>432</v>
       </c>
       <c r="H157" s="1" t="str">
@@ -5330,25 +5323,25 @@
       </c>
     </row>
     <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="0" t="s">
+      <c r="A158" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C158" s="0" t="s">
+      <c r="C158" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D158" s="0" t="n">
+      <c r="D158" s="1" t="n">
         <v>2014</v>
       </c>
-      <c r="E158" s="0" t="s">
-        <v>236</v>
-      </c>
-      <c r="F158" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G158" s="0" t="n">
+      <c r="E158" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G158" s="1" t="n">
         <v>317</v>
       </c>
       <c r="H158" s="1" t="str">
@@ -5357,25 +5350,25 @@
       </c>
     </row>
     <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="0" t="s">
+      <c r="A159" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C159" s="0" t="s">
+      <c r="C159" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D159" s="0" t="n">
+      <c r="D159" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E159" s="0" t="s">
-        <v>237</v>
-      </c>
-      <c r="F159" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G159" s="0" t="n">
+      <c r="E159" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G159" s="1" t="n">
         <v>298</v>
       </c>
       <c r="H159" s="1" t="str">
@@ -5384,25 +5377,25 @@
       </c>
     </row>
     <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="0" t="s">
+      <c r="A160" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C160" s="0" t="s">
+      <c r="C160" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D160" s="0" t="n">
+      <c r="D160" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E160" s="0" t="s">
-        <v>238</v>
-      </c>
-      <c r="F160" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G160" s="0" t="n">
+      <c r="E160" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G160" s="1" t="n">
         <v>87</v>
       </c>
       <c r="H160" s="1" t="str">
@@ -5411,25 +5404,25 @@
       </c>
     </row>
     <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="0" t="s">
+      <c r="A161" s="1" t="s">
         <v>178</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C161" s="0" t="s">
+      <c r="C161" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D161" s="0" t="n">
+      <c r="D161" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E161" s="0" t="s">
-        <v>239</v>
-      </c>
-      <c r="F161" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G161" s="0" t="n">
+      <c r="E161" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G161" s="1" t="n">
         <v>312</v>
       </c>
       <c r="H161" s="1" t="str">
@@ -5438,25 +5431,25 @@
       </c>
     </row>
     <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="0" t="s">
+      <c r="A162" s="1" t="s">
         <v>178</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C162" s="0" t="s">
+      <c r="C162" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D162" s="0" t="n">
+      <c r="D162" s="1" t="n">
         <v>2010</v>
       </c>
-      <c r="E162" s="0" t="s">
-        <v>240</v>
-      </c>
-      <c r="F162" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G162" s="0" t="n">
+      <c r="E162" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G162" s="1" t="n">
         <v>208</v>
       </c>
       <c r="H162" s="1" t="str">
@@ -5465,25 +5458,25 @@
       </c>
     </row>
     <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="0" t="s">
+      <c r="A163" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C163" s="0" t="s">
+      <c r="C163" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D163" s="0" t="n">
+      <c r="D163" s="1" t="n">
         <v>2008</v>
       </c>
-      <c r="E163" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="F163" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G163" s="0" t="n">
+      <c r="E163" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G163" s="1" t="n">
         <v>752</v>
       </c>
       <c r="H163" s="1" t="str">
@@ -5492,25 +5485,25 @@
       </c>
     </row>
     <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="0" t="s">
+      <c r="A164" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C164" s="0" t="s">
+      <c r="C164" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D164" s="0" t="n">
+      <c r="D164" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E164" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="F164" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G164" s="0" t="n">
+      <c r="E164" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G164" s="1" t="n">
         <v>463</v>
       </c>
       <c r="H164" s="1" t="str">
@@ -5519,25 +5512,25 @@
       </c>
     </row>
     <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="0" t="s">
+      <c r="A165" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C165" s="0" t="s">
+      <c r="C165" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D165" s="1" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E165" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D165" s="0" t="n">
-        <v>2011</v>
-      </c>
-      <c r="E165" s="0" t="s">
-        <v>244</v>
-      </c>
-      <c r="F165" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G165" s="0" t="n">
+      <c r="F165" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G165" s="1" t="n">
         <v>403</v>
       </c>
       <c r="H165" s="1" t="str">
@@ -5546,25 +5539,25 @@
       </c>
     </row>
     <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="0" t="s">
+      <c r="A166" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C166" s="0" t="s">
+      <c r="C166" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D166" s="0" t="n">
+      <c r="D166" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E166" s="0" t="s">
+      <c r="E166" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F166" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G166" s="0" t="n">
+      <c r="F166" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G166" s="1" t="n">
         <v>263</v>
       </c>
       <c r="H166" s="1" t="str">
@@ -5573,25 +5566,25 @@
       </c>
     </row>
     <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="0" t="s">
+      <c r="A167" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C167" s="0" t="s">
+      <c r="C167" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D167" s="0" t="n">
+      <c r="D167" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E167" s="0" t="s">
-        <v>245</v>
-      </c>
-      <c r="F167" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G167" s="0" t="n">
+      <c r="E167" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G167" s="1" t="n">
         <v>98</v>
       </c>
       <c r="H167" s="1" t="str">
@@ -5600,25 +5593,25 @@
       </c>
     </row>
     <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="0" t="s">
+      <c r="A168" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C168" s="0" t="s">
+      <c r="C168" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D168" s="0" t="n">
+      <c r="D168" s="1" t="n">
         <v>2016</v>
       </c>
-      <c r="E168" s="0" t="s">
-        <v>246</v>
-      </c>
-      <c r="F168" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G168" s="0" t="n">
+      <c r="E168" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G168" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H168" s="1" t="str">
@@ -5627,25 +5620,25 @@
       </c>
     </row>
     <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="0" t="s">
+      <c r="A169" s="1" t="s">
         <v>151</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C169" s="0" t="s">
+      <c r="C169" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D169" s="0" t="n">
+      <c r="D169" s="1" t="n">
         <v>2008</v>
       </c>
-      <c r="E169" s="0" t="s">
-        <v>247</v>
-      </c>
-      <c r="F169" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G169" s="0" t="n">
+      <c r="E169" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G169" s="1" t="n">
         <v>620</v>
       </c>
       <c r="H169" s="1" t="str">
@@ -5654,25 +5647,25 @@
       </c>
     </row>
     <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="0" t="s">
+      <c r="A170" s="1" t="s">
         <v>151</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C170" s="0" t="s">
-        <v>243</v>
-      </c>
-      <c r="D170" s="0" t="n">
+      <c r="C170" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D170" s="1" t="n">
         <v>2011</v>
       </c>
-      <c r="E170" s="0" t="s">
-        <v>248</v>
-      </c>
-      <c r="F170" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G170" s="0" t="n">
+      <c r="E170" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G170" s="1" t="n">
         <v>391</v>
       </c>
       <c r="H170" s="1" t="str">
@@ -5681,25 +5674,25 @@
       </c>
     </row>
     <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="0" t="s">
+      <c r="A171" s="1" t="s">
         <v>151</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C171" s="0" t="s">
+      <c r="C171" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D171" s="0" t="n">
+      <c r="D171" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E171" s="0" t="s">
-        <v>249</v>
-      </c>
-      <c r="F171" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G171" s="0" t="n">
+      <c r="E171" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G171" s="1" t="n">
         <v>201</v>
       </c>
       <c r="H171" s="1" t="str">
@@ -5708,25 +5701,25 @@
       </c>
     </row>
     <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="0" t="s">
+      <c r="A172" s="1" t="s">
         <v>151</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C172" s="0" t="s">
+      <c r="C172" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D172" s="0" t="n">
+      <c r="D172" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E172" s="0" t="s">
-        <v>250</v>
-      </c>
-      <c r="F172" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G172" s="0" t="n">
+      <c r="E172" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G172" s="1" t="n">
         <v>124</v>
       </c>
       <c r="H172" s="1" t="str">
@@ -5735,25 +5728,25 @@
       </c>
     </row>
     <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="0" t="s">
+      <c r="A173" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D173" s="1" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E173" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C173" s="0" t="s">
-        <v>128</v>
-      </c>
-      <c r="D173" s="0" t="n">
-        <v>2012</v>
-      </c>
-      <c r="E173" s="0" t="s">
-        <v>252</v>
-      </c>
-      <c r="F173" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G173" s="0" t="n">
+      <c r="F173" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G173" s="1" t="n">
         <v>316</v>
       </c>
       <c r="H173" s="1" t="str">
@@ -5762,25 +5755,25 @@
       </c>
     </row>
     <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="0" t="s">
-        <v>251</v>
+      <c r="A174" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C174" s="0" t="s">
+      <c r="C174" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D174" s="0" t="n">
+      <c r="D174" s="1" t="n">
         <v>2016</v>
       </c>
-      <c r="E174" s="0" t="s">
-        <v>253</v>
-      </c>
-      <c r="F174" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G174" s="0" t="n">
+      <c r="E174" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G174" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H174" s="1" t="str">
@@ -5789,25 +5782,25 @@
       </c>
     </row>
     <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="0" t="s">
+      <c r="A175" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C175" s="0" t="s">
+      <c r="C175" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D175" s="0" t="n">
+      <c r="D175" s="1" t="n">
         <v>2008</v>
       </c>
-      <c r="E175" s="0" t="s">
-        <v>254</v>
-      </c>
-      <c r="F175" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G175" s="0" t="n">
+      <c r="E175" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G175" s="1" t="n">
         <v>425</v>
       </c>
       <c r="H175" s="1" t="str">
@@ -5854,19 +5847,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>256</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/data/resultats_xlsx.xlsx
+++ b/data/resultats_xlsx.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="279">
   <si>
     <t xml:space="preserve">EPREUVE</t>
   </si>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">00:51.80</t>
   </si>
   <si>
-    <t xml:space="preserve">50 papillon Dames</t>
+    <t xml:space="preserve">50 Papillon Dames</t>
   </si>
   <si>
     <t xml:space="preserve">00:40.77</t>
@@ -254,9 +254,6 @@
     <t xml:space="preserve">00:41.37</t>
   </si>
   <si>
-    <t xml:space="preserve">50 brasse Messieurs</t>
-  </si>
-  <si>
     <t xml:space="preserve">00:41.23</t>
   </si>
   <si>
@@ -557,9 +554,6 @@
     <t xml:space="preserve">04:19.34</t>
   </si>
   <si>
-    <t xml:space="preserve">50 Papillon Dames</t>
-  </si>
-  <si>
     <t xml:space="preserve">00:52.54</t>
   </si>
   <si>
@@ -783,6 +777,75 @@
   </si>
   <si>
     <t xml:space="preserve">00:39.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:28.87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:31.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:33.46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:18.61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:17.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:09.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:18.58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06:28.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06:17.46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">800 Nage Libre Messieurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:57.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:40.96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:41.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:44.42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:41.34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:31.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:34.34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 Papillon Messieurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:27.38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200 4 Nages Messieurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03:05.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03:23.10</t>
   </si>
   <si>
     <t xml:space="preserve">NOM_PRENOM</t>
@@ -872,7 +935,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -886,6 +949,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2002,7 +2069,7 @@
         <v>Avenirs</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>74</v>
       </c>
@@ -2029,7 +2096,7 @@
         <v>Seniors</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>74</v>
       </c>
@@ -2056,9 +2123,10 @@
         <v>Juniors</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
-        <v>77</v>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="str">
+        <f aca="false">"50 Brasse Messieurs"</f>
+        <v>50 Brasse Messieurs</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>9</v>
@@ -2070,7 +2138,7 @@
         <v>1983</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>45778</v>
@@ -2083,9 +2151,10 @@
         <v>Master C4</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
-        <v>77</v>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="str">
+        <f aca="false">"50 Brasse Messieurs"</f>
+        <v>50 Brasse Messieurs</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>9</v>
@@ -2097,7 +2166,7 @@
         <v>1993</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>45778</v>
@@ -2110,9 +2179,10 @@
         <v>Master C2</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
-        <v>77</v>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="str">
+        <f aca="false">"50 Brasse Messieurs"</f>
+        <v>50 Brasse Messieurs</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>9</v>
@@ -2124,7 +2194,7 @@
         <v>2010</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>45778</v>
@@ -2137,9 +2207,10 @@
         <v>Juniors</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
-        <v>77</v>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="str">
+        <f aca="false">"50 Brasse Messieurs"</f>
+        <v>50 Brasse Messieurs</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>9</v>
@@ -2151,7 +2222,7 @@
         <v>2012</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>45778</v>
@@ -2166,7 +2237,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>47</v>
@@ -2178,7 +2249,7 @@
         <v>2002</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>45778</v>
@@ -2193,7 +2264,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>47</v>
@@ -2205,7 +2276,7 @@
         <v>2011</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>45778</v>
@@ -2220,7 +2291,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>47</v>
@@ -2232,7 +2303,7 @@
         <v>2010</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>45778</v>
@@ -2241,12 +2312,12 @@
         <v>429</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>47</v>
@@ -2258,7 +2329,7 @@
         <v>2012</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>45778</v>
@@ -2273,7 +2344,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>47</v>
@@ -2285,7 +2356,7 @@
         <v>2013</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>45778</v>
@@ -2300,7 +2371,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>47</v>
@@ -2312,7 +2383,7 @@
         <v>2012</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>45778</v>
@@ -2327,7 +2398,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>47</v>
@@ -2339,7 +2410,7 @@
         <v>2012</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>45778</v>
@@ -2354,7 +2425,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>47</v>
@@ -2366,7 +2437,7 @@
         <v>2013</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>45778</v>
@@ -2381,7 +2452,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>47</v>
@@ -2393,7 +2464,7 @@
         <v>2014</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>45778</v>
@@ -2408,7 +2479,7 @@
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>47</v>
@@ -2420,7 +2491,7 @@
         <v>2015</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>45778</v>
@@ -2447,10 +2518,10 @@
         <v>2012</v>
       </c>
       <c r="E51" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>539</v>
@@ -2474,10 +2545,10 @@
         <v>2012</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>398</v>
@@ -2495,16 +2566,16 @@
         <v>47</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D53" s="1" t="n">
         <v>2010</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>388</v>
@@ -2522,16 +2593,16 @@
         <v>47</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D54" s="1" t="n">
         <v>2014</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>377</v>
@@ -2555,10 +2626,10 @@
         <v>2013</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>354</v>
@@ -2582,10 +2653,10 @@
         <v>2012</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>344</v>
@@ -2609,10 +2680,10 @@
         <v>2011</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>334</v>
@@ -2630,16 +2701,16 @@
         <v>47</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D58" s="1" t="n">
         <v>2014</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G58" s="1" t="n">
         <v>318</v>
@@ -2663,10 +2734,10 @@
         <v>2014</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G59" s="1" t="n">
         <v>204</v>
@@ -2684,16 +2755,16 @@
         <v>47</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D60" s="1" t="n">
         <v>2010</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>158</v>
@@ -2711,16 +2782,16 @@
         <v>47</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D61" s="1" t="n">
         <v>2013</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G61" s="1" t="n">
         <v>144</v>
@@ -2732,7 +2803,7 @@
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>47</v>
@@ -2744,10 +2815,10 @@
         <v>2012</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G62" s="1" t="n">
         <v>493</v>
@@ -2759,22 +2830,22 @@
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D63" s="1" t="n">
         <v>2010</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G63" s="1" t="n">
         <v>224</v>
@@ -2786,7 +2857,7 @@
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>47</v>
@@ -2798,10 +2869,10 @@
         <v>2012</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G64" s="1" t="n">
         <v>473</v>
@@ -2813,7 +2884,7 @@
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>47</v>
@@ -2825,10 +2896,10 @@
         <v>2011</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G65" s="1" t="n">
         <v>390</v>
@@ -2840,22 +2911,22 @@
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D66" s="1" t="n">
         <v>2010</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G66" s="1" t="n">
         <v>357</v>
@@ -2867,7 +2938,7 @@
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>47</v>
@@ -2879,10 +2950,10 @@
         <v>2013</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G67" s="1" t="n">
         <v>340</v>
@@ -2894,22 +2965,22 @@
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D68" s="1" t="n">
         <v>2013</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G68" s="1" t="n">
         <v>332</v>
@@ -2921,7 +2992,7 @@
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>47</v>
@@ -2933,10 +3004,10 @@
         <v>2012</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G69" s="1" t="n">
         <v>329</v>
@@ -2948,22 +3019,22 @@
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D70" s="1" t="n">
         <v>2014</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G70" s="1" t="n">
         <v>303</v>
@@ -2975,7 +3046,7 @@
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>47</v>
@@ -2987,10 +3058,10 @@
         <v>2012</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G71" s="1" t="n">
         <v>263</v>
@@ -3002,22 +3073,22 @@
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D72" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G72" s="1" t="n">
         <v>242</v>
@@ -3029,22 +3100,22 @@
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D73" s="1" t="n">
         <v>2014</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G73" s="1" t="n">
         <v>217</v>
@@ -3056,7 +3127,7 @@
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>47</v>
@@ -3068,10 +3139,10 @@
         <v>2014</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G74" s="1" t="n">
         <v>178</v>
@@ -3089,16 +3160,16 @@
         <v>9</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D75" s="1" t="n">
         <v>2008</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G75" s="1" t="n">
         <v>588</v>
@@ -3116,16 +3187,16 @@
         <v>9</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D76" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G76" s="1" t="n">
         <v>297</v>
@@ -3149,10 +3220,10 @@
         <v>2015</v>
       </c>
       <c r="E77" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F77" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="G77" s="1" t="n">
         <v>93</v>
@@ -3164,22 +3235,22 @@
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D78" s="1" t="n">
         <v>2014</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G78" s="1" t="n">
         <v>172</v>
@@ -3191,22 +3262,22 @@
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D79" s="1" t="n">
         <v>2014</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G79" s="1" t="n">
         <v>169</v>
@@ -3218,7 +3289,7 @@
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>47</v>
@@ -3230,10 +3301,10 @@
         <v>2014</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G80" s="1" t="n">
         <v>86</v>
@@ -3245,22 +3316,22 @@
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D81" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G81" s="1" t="n">
         <v>68</v>
@@ -3272,22 +3343,22 @@
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D82" s="1" t="n">
         <v>2014</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G82" s="1" t="n">
         <v>314</v>
@@ -3299,22 +3370,22 @@
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D83" s="1" t="n">
         <v>2014</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G83" s="1" t="n">
         <v>272</v>
@@ -3326,7 +3397,7 @@
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>47</v>
@@ -3338,10 +3409,10 @@
         <v>2014</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G84" s="1" t="n">
         <v>234</v>
@@ -3353,7 +3424,7 @@
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>47</v>
@@ -3365,10 +3436,10 @@
         <v>2015</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G85" s="1" t="n">
         <v>176</v>
@@ -3380,22 +3451,22 @@
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D86" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G86" s="1" t="n">
         <v>10</v>
@@ -3413,16 +3484,16 @@
         <v>9</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D87" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G87" s="1" t="n">
         <v>71</v>
@@ -3440,16 +3511,16 @@
         <v>9</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D88" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G88" s="1" t="n">
         <v>26</v>
@@ -3467,16 +3538,16 @@
         <v>9</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D89" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G89" s="1" t="n">
         <v>1</v>
@@ -3494,16 +3565,16 @@
         <v>9</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D90" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G90" s="1" t="n">
         <v>1</v>
@@ -3515,22 +3586,22 @@
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D91" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G91" s="1" t="n">
         <v>146</v>
@@ -3542,22 +3613,22 @@
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D92" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G92" s="1" t="n">
         <v>78</v>
@@ -3569,22 +3640,22 @@
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D93" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G93" s="1" t="n">
         <v>1</v>
@@ -3596,22 +3667,22 @@
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D94" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G94" s="1" t="n">
         <v>1</v>
@@ -3629,16 +3700,16 @@
         <v>47</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D95" s="1" t="n">
         <v>2016</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G95" s="1" t="n">
         <v>1</v>
@@ -3656,16 +3727,16 @@
         <v>47</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D96" s="1" t="n">
         <v>2017</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G96" s="1" t="n">
         <v>1</v>
@@ -3677,22 +3748,22 @@
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D97" s="1" t="n">
         <v>2016</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G97" s="1" t="n">
         <v>71</v>
@@ -3704,22 +3775,22 @@
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D98" s="1" t="n">
         <v>2017</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G98" s="1" t="n">
         <v>7</v>
@@ -3737,16 +3808,16 @@
         <v>9</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D99" s="1" t="n">
         <v>2016</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G99" s="1" t="n">
         <v>1</v>
@@ -3758,22 +3829,22 @@
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D100" s="1" t="n">
         <v>2016</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G100" s="1" t="n">
         <v>11</v>
@@ -3785,7 +3856,7 @@
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>47</v>
@@ -3797,10 +3868,10 @@
         <v>2013</v>
       </c>
       <c r="E101" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F101" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G101" s="1" t="n">
         <v>472</v>
@@ -3812,7 +3883,7 @@
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>47</v>
@@ -3824,10 +3895,10 @@
         <v>2013</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G102" s="1" t="n">
         <v>391</v>
@@ -3839,22 +3910,22 @@
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D103" s="1" t="n">
         <v>2010</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G103" s="1" t="n">
         <v>244</v>
@@ -3866,7 +3937,7 @@
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>47</v>
@@ -3878,10 +3949,10 @@
         <v>2014</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G104" s="1" t="n">
         <v>84</v>
@@ -3893,7 +3964,7 @@
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>47</v>
@@ -3905,10 +3976,10 @@
         <v>2012</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G105" s="1" t="n">
         <v>321</v>
@@ -3920,22 +3991,22 @@
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="D106" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G106" s="1" t="n">
         <v>499</v>
@@ -3947,7 +4018,7 @@
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>47</v>
@@ -3959,10 +4030,10 @@
         <v>2012</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G107" s="1" t="n">
         <v>486</v>
@@ -3974,7 +4045,7 @@
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>47</v>
@@ -3986,10 +4057,10 @@
         <v>2014</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G108" s="1" t="n">
         <v>264</v>
@@ -4001,7 +4072,7 @@
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>178</v>
+        <v>74</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>47</v>
@@ -4013,10 +4084,10 @@
         <v>2013</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G109" s="1" t="n">
         <v>134</v>
@@ -4028,22 +4099,22 @@
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>178</v>
+        <v>74</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D110" s="1" t="n">
         <v>2010</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G110" s="1" t="n">
         <v>60</v>
@@ -4055,22 +4126,22 @@
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D111" s="1" t="n">
         <v>2008</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G111" s="1" t="n">
         <v>460</v>
@@ -4082,22 +4153,22 @@
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D112" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G112" s="1" t="n">
         <v>235</v>
@@ -4109,22 +4180,22 @@
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D113" s="1" t="n">
         <v>2008</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G113" s="1" t="n">
         <v>460</v>
@@ -4142,16 +4213,16 @@
         <v>47</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D114" s="1" t="n">
         <v>2016</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G114" s="1" t="n">
         <v>169</v>
@@ -4169,16 +4240,16 @@
         <v>47</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D115" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G115" s="1" t="n">
         <v>3</v>
@@ -4190,7 +4261,7 @@
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>47</v>
@@ -4202,10 +4273,10 @@
         <v>2015</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G116" s="1" t="n">
         <v>141</v>
@@ -4217,22 +4288,22 @@
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D117" s="1" t="n">
         <v>2016</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G117" s="1" t="n">
         <v>123</v>
@@ -4244,22 +4315,22 @@
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D118" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G118" s="1" t="n">
         <v>93</v>
@@ -4271,7 +4342,7 @@
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>47</v>
@@ -4283,10 +4354,10 @@
         <v>2015</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G119" s="1" t="n">
         <v>299</v>
@@ -4304,16 +4375,16 @@
         <v>9</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D120" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G120" s="1" t="n">
         <v>246</v>
@@ -4331,16 +4402,16 @@
         <v>9</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D121" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G121" s="1" t="n">
         <v>121</v>
@@ -4358,16 +4429,16 @@
         <v>9</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D122" s="1" t="n">
         <v>2016</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G122" s="1" t="n">
         <v>52</v>
@@ -4385,16 +4456,16 @@
         <v>9</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D123" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G123" s="1" t="n">
         <v>39</v>
@@ -4412,16 +4483,16 @@
         <v>9</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D124" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G124" s="1" t="n">
         <v>1</v>
@@ -4433,22 +4504,22 @@
     </row>
     <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D125" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G125" s="1" t="n">
         <v>184</v>
@@ -4460,22 +4531,22 @@
     </row>
     <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D126" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G126" s="1" t="n">
         <v>63</v>
@@ -4487,22 +4558,22 @@
     </row>
     <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D127" s="1" t="n">
         <v>2016</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G127" s="1" t="n">
         <v>54</v>
@@ -4514,22 +4585,22 @@
     </row>
     <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D128" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G128" s="1" t="n">
         <v>16</v>
@@ -4541,22 +4612,22 @@
     </row>
     <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D129" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G129" s="1" t="n">
         <v>12</v>
@@ -4580,10 +4651,10 @@
         <v>2013</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G130" s="1" t="n">
         <v>691</v>
@@ -4607,10 +4678,10 @@
         <v>2013</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G131" s="1" t="n">
         <v>498</v>
@@ -4628,16 +4699,16 @@
         <v>47</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D132" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G132" s="1" t="n">
         <v>493</v>
@@ -4661,10 +4732,10 @@
         <v>2012</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G133" s="1" t="n">
         <v>360</v>
@@ -4682,16 +4753,16 @@
         <v>47</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D134" s="1" t="n">
         <v>2010</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G134" s="1" t="n">
         <v>325</v>
@@ -4703,22 +4774,22 @@
     </row>
     <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D135" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G135" s="1" t="n">
         <v>647</v>
@@ -4730,7 +4801,7 @@
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>47</v>
@@ -4742,10 +4813,10 @@
         <v>2012</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G136" s="1" t="n">
         <v>539</v>
@@ -4757,7 +4828,7 @@
     </row>
     <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>47</v>
@@ -4769,10 +4840,10 @@
         <v>2013</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G137" s="1" t="n">
         <v>528</v>
@@ -4784,22 +4855,22 @@
     </row>
     <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D138" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G138" s="1" t="n">
         <v>431</v>
@@ -4811,7 +4882,7 @@
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>47</v>
@@ -4823,10 +4894,10 @@
         <v>2012</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G139" s="1" t="n">
         <v>319</v>
@@ -4838,7 +4909,7 @@
     </row>
     <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>47</v>
@@ -4850,10 +4921,10 @@
         <v>2013</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G140" s="1" t="n">
         <v>299</v>
@@ -4865,22 +4936,22 @@
     </row>
     <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D141" s="1" t="n">
         <v>2010</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G141" s="1" t="n">
         <v>247</v>
@@ -4898,16 +4969,16 @@
         <v>9</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D142" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G142" s="1" t="n">
         <v>516</v>
@@ -4919,22 +4990,22 @@
     </row>
     <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D143" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G143" s="1" t="n">
         <v>207</v>
@@ -4958,10 +5029,10 @@
         <v>2012</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G144" s="1" t="n">
         <v>652</v>
@@ -4979,16 +5050,16 @@
         <v>47</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D145" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G145" s="1" t="n">
         <v>511</v>
@@ -5012,10 +5083,10 @@
         <v>2013</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G146" s="1" t="n">
         <v>497</v>
@@ -5039,10 +5110,10 @@
         <v>2012</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G147" s="1" t="n">
         <v>377</v>
@@ -5060,16 +5131,16 @@
         <v>47</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D148" s="1" t="n">
         <v>2010</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G148" s="1" t="n">
         <v>321</v>
@@ -5087,16 +5158,16 @@
         <v>47</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D149" s="1" t="n">
         <v>2016</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G149" s="1" t="n">
         <v>278</v>
@@ -5120,10 +5191,10 @@
         <v>2015</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G150" s="1" t="n">
         <v>244</v>
@@ -5147,10 +5218,10 @@
         <v>2014</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G151" s="1" t="n">
         <v>218</v>
@@ -5168,16 +5239,16 @@
         <v>47</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D152" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G152" s="1" t="n">
         <v>5</v>
@@ -5189,7 +5260,7 @@
     </row>
     <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>47</v>
@@ -5201,10 +5272,10 @@
         <v>2012</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G153" s="1" t="n">
         <v>583</v>
@@ -5216,22 +5287,22 @@
     </row>
     <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D154" s="1" t="n">
         <v>2016</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G154" s="1" t="n">
         <v>246</v>
@@ -5243,22 +5314,22 @@
     </row>
     <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D155" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G155" s="1" t="n">
         <v>575</v>
@@ -5270,7 +5341,7 @@
     </row>
     <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>47</v>
@@ -5282,10 +5353,10 @@
         <v>2012</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G156" s="1" t="n">
         <v>456</v>
@@ -5297,7 +5368,7 @@
     </row>
     <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>47</v>
@@ -5309,10 +5380,10 @@
         <v>2013</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G157" s="1" t="n">
         <v>432</v>
@@ -5324,7 +5395,7 @@
     </row>
     <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>47</v>
@@ -5336,10 +5407,10 @@
         <v>2014</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G158" s="1" t="n">
         <v>317</v>
@@ -5351,7 +5422,7 @@
     </row>
     <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>47</v>
@@ -5363,10 +5434,10 @@
         <v>2015</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G159" s="1" t="n">
         <v>298</v>
@@ -5378,22 +5449,22 @@
     </row>
     <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D160" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G160" s="1" t="n">
         <v>87</v>
@@ -5405,7 +5476,7 @@
     </row>
     <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>178</v>
+        <v>74</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>47</v>
@@ -5417,10 +5488,10 @@
         <v>2012</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G161" s="1" t="n">
         <v>312</v>
@@ -5432,22 +5503,22 @@
     </row>
     <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>178</v>
+        <v>74</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D162" s="1" t="n">
         <v>2010</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G162" s="1" t="n">
         <v>208</v>
@@ -5465,16 +5536,16 @@
         <v>9</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D163" s="1" t="n">
         <v>2008</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G163" s="1" t="n">
         <v>752</v>
@@ -5492,16 +5563,16 @@
         <v>9</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D164" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G164" s="1" t="n">
         <v>463</v>
@@ -5519,16 +5590,16 @@
         <v>9</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D165" s="1" t="n">
         <v>2011</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G165" s="1" t="n">
         <v>403</v>
@@ -5546,16 +5617,16 @@
         <v>9</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D166" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G166" s="1" t="n">
         <v>263</v>
@@ -5573,16 +5644,16 @@
         <v>9</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D167" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G167" s="1" t="n">
         <v>98</v>
@@ -5600,16 +5671,16 @@
         <v>9</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D168" s="1" t="n">
         <v>2016</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G168" s="1" t="n">
         <v>23</v>
@@ -5621,22 +5692,22 @@
     </row>
     <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D169" s="1" t="n">
         <v>2008</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G169" s="1" t="n">
         <v>620</v>
@@ -5648,22 +5719,22 @@
     </row>
     <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D170" s="1" t="n">
         <v>2011</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G170" s="1" t="n">
         <v>391</v>
@@ -5675,22 +5746,22 @@
     </row>
     <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D171" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G171" s="1" t="n">
         <v>201</v>
@@ -5702,22 +5773,22 @@
     </row>
     <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D172" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G172" s="1" t="n">
         <v>124</v>
@@ -5729,22 +5800,22 @@
     </row>
     <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D173" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G173" s="1" t="n">
         <v>316</v>
@@ -5756,22 +5827,22 @@
     </row>
     <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D174" s="1" t="n">
         <v>2016</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G174" s="1" t="n">
         <v>1</v>
@@ -5789,16 +5860,16 @@
         <v>9</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D175" s="1" t="n">
         <v>2008</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G175" s="1" t="n">
         <v>425</v>
@@ -5809,13 +5880,517 @@
       </c>
     </row>
     <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B176" s="1"/>
+      <c r="A176" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C176" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D176" s="0" t="n">
+        <v>1983</v>
+      </c>
+      <c r="E176" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G176" s="0" t="n">
+        <v>943</v>
+      </c>
+      <c r="H176" s="1" t="str">
+        <f aca="false">IF((YEAR(F176)-D176)&lt;=11,"Avenirs",IF((YEAR(F176)-D176)&lt;=13,"Benjamins",IF((YEAR(F176)-D176)&lt;=18,"Juniors",IF((YEAR(F176)-D176)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F176)-D176-25)/5,0)))))</f>
+        <v>Master C4</v>
+      </c>
     </row>
     <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B177" s="1"/>
+      <c r="A177" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C177" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="D177" s="0" t="n">
+        <v>1978</v>
+      </c>
+      <c r="E177" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G177" s="0" t="n">
+        <v>835</v>
+      </c>
+      <c r="H177" s="1" t="str">
+        <f aca="false">IF((YEAR(F177)-D177)&lt;=11,"Avenirs",IF((YEAR(F177)-D177)&lt;=13,"Benjamins",IF((YEAR(F177)-D177)&lt;=18,"Juniors",IF((YEAR(F177)-D177)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F177)-D177-25)/5,0)))))</f>
+        <v>Master C5</v>
+      </c>
     </row>
     <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B178" s="1"/>
+      <c r="A178" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C178" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D178" s="0" t="n">
+        <v>1996</v>
+      </c>
+      <c r="E178" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G178" s="0" t="n">
+        <v>612</v>
+      </c>
+      <c r="H178" s="1" t="str">
+        <f aca="false">IF((YEAR(F178)-D178)&lt;=11,"Avenirs",IF((YEAR(F178)-D178)&lt;=13,"Benjamins",IF((YEAR(F178)-D178)&lt;=18,"Juniors",IF((YEAR(F178)-D178)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F178)-D178-25)/5,0)))))</f>
+        <v>Master C1</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C179" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D179" s="0" t="n">
+        <v>1967</v>
+      </c>
+      <c r="E179" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G179" s="0" t="n">
+        <v>655</v>
+      </c>
+      <c r="H179" s="1" t="str">
+        <f aca="false">IF((YEAR(F179)-D179)&lt;=11,"Avenirs",IF((YEAR(F179)-D179)&lt;=13,"Benjamins",IF((YEAR(F179)-D179)&lt;=18,"Juniors",IF((YEAR(F179)-D179)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F179)-D179-25)/5,0)))))</f>
+        <v>Master C7</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C180" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="D180" s="0" t="n">
+        <v>1979</v>
+      </c>
+      <c r="E180" s="0" t="s">
+        <v>257</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G180" s="0" t="n">
+        <v>590</v>
+      </c>
+      <c r="H180" s="1" t="str">
+        <f aca="false">IF((YEAR(F180)-D180)&lt;=11,"Avenirs",IF((YEAR(F180)-D180)&lt;=13,"Benjamins",IF((YEAR(F180)-D180)&lt;=18,"Juniors",IF((YEAR(F180)-D180)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F180)-D180-25)/5,0)))))</f>
+        <v>Master C5</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C181" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D181" s="0" t="n">
+        <v>1983</v>
+      </c>
+      <c r="E181" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G181" s="0" t="n">
+        <v>766</v>
+      </c>
+      <c r="H181" s="1" t="str">
+        <f aca="false">IF((YEAR(F181)-D181)&lt;=11,"Avenirs",IF((YEAR(F181)-D181)&lt;=13,"Benjamins",IF((YEAR(F181)-D181)&lt;=18,"Juniors",IF((YEAR(F181)-D181)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F181)-D181-25)/5,0)))))</f>
+        <v>Master C4</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C182" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D182" s="0" t="n">
+        <v>1996</v>
+      </c>
+      <c r="E182" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="F182" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G182" s="0" t="n">
+        <v>475</v>
+      </c>
+      <c r="H182" s="1" t="str">
+        <f aca="false">IF((YEAR(F182)-D182)&lt;=11,"Avenirs",IF((YEAR(F182)-D182)&lt;=13,"Benjamins",IF((YEAR(F182)-D182)&lt;=18,"Juniors",IF((YEAR(F182)-D182)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F182)-D182-25)/5,0)))))</f>
+        <v>Master C1</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C183" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D183" s="0" t="n">
+        <v>1967</v>
+      </c>
+      <c r="E183" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G183" s="0" t="n">
+        <v>484</v>
+      </c>
+      <c r="H183" s="1" t="str">
+        <f aca="false">IF((YEAR(F183)-D183)&lt;=11,"Avenirs",IF((YEAR(F183)-D183)&lt;=13,"Benjamins",IF((YEAR(F183)-D183)&lt;=18,"Juniors",IF((YEAR(F183)-D183)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F183)-D183-25)/5,0)))))</f>
+        <v>Master C7</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C184" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D184" s="0" t="n">
+        <v>1973</v>
+      </c>
+      <c r="E184" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G184" s="0" t="n">
+        <v>451</v>
+      </c>
+      <c r="H184" s="1" t="str">
+        <f aca="false">IF((YEAR(F184)-D184)&lt;=11,"Avenirs",IF((YEAR(F184)-D184)&lt;=13,"Benjamins",IF((YEAR(F184)-D184)&lt;=18,"Juniors",IF((YEAR(F184)-D184)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F184)-D184-25)/5,0)))))</f>
+        <v>Master C6</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C185" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D185" s="0" t="n">
+        <v>1973</v>
+      </c>
+      <c r="E185" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G185" s="0" t="n">
+        <v>432</v>
+      </c>
+      <c r="H185" s="1" t="str">
+        <f aca="false">IF((YEAR(F185)-D185)&lt;=11,"Avenirs",IF((YEAR(F185)-D185)&lt;=13,"Benjamins",IF((YEAR(F185)-D185)&lt;=18,"Juniors",IF((YEAR(F185)-D185)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F185)-D185-25)/5,0)))))</f>
+        <v>Master C6</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C186" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="D186" s="0" t="n">
+        <v>1993</v>
+      </c>
+      <c r="E186" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G186" s="0" t="n">
+        <v>654</v>
+      </c>
+      <c r="H186" s="1" t="str">
+        <f aca="false">IF((YEAR(F186)-D186)&lt;=11,"Avenirs",IF((YEAR(F186)-D186)&lt;=13,"Benjamins",IF((YEAR(F186)-D186)&lt;=18,"Juniors",IF((YEAR(F186)-D186)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F186)-D186-25)/5,0)))))</f>
+        <v>Master C2</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C187" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="D187" s="0" t="n">
+        <v>1978</v>
+      </c>
+      <c r="E187" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G187" s="0" t="n">
+        <v>697</v>
+      </c>
+      <c r="H187" s="1" t="str">
+        <f aca="false">IF((YEAR(F187)-D187)&lt;=11,"Avenirs",IF((YEAR(F187)-D187)&lt;=13,"Benjamins",IF((YEAR(F187)-D187)&lt;=18,"Juniors",IF((YEAR(F187)-D187)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F187)-D187-25)/5,0)))))</f>
+        <v>Master C5</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C188" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D188" s="0" t="n">
+        <v>1996</v>
+      </c>
+      <c r="E188" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="F188" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G188" s="0" t="n">
+        <v>524</v>
+      </c>
+      <c r="H188" s="1" t="str">
+        <f aca="false">IF((YEAR(F188)-D188)&lt;=11,"Avenirs",IF((YEAR(F188)-D188)&lt;=13,"Benjamins",IF((YEAR(F188)-D188)&lt;=18,"Juniors",IF((YEAR(F188)-D188)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F188)-D188-25)/5,0)))))</f>
+        <v>Master C1</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C189" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D189" s="0" t="n">
+        <v>1983</v>
+      </c>
+      <c r="E189" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G189" s="0" t="n">
+        <v>696</v>
+      </c>
+      <c r="H189" s="1" t="str">
+        <f aca="false">IF((YEAR(F189)-D189)&lt;=11,"Avenirs",IF((YEAR(F189)-D189)&lt;=13,"Benjamins",IF((YEAR(F189)-D189)&lt;=18,"Juniors",IF((YEAR(F189)-D189)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F189)-D189-25)/5,0)))))</f>
+        <v>Master C4</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C190" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="D190" s="0" t="n">
+        <v>1993</v>
+      </c>
+      <c r="E190" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="F190" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G190" s="0" t="n">
+        <v>609</v>
+      </c>
+      <c r="H190" s="1" t="str">
+        <f aca="false">IF((YEAR(F190)-D190)&lt;=11,"Avenirs",IF((YEAR(F190)-D190)&lt;=13,"Benjamins",IF((YEAR(F190)-D190)&lt;=18,"Juniors",IF((YEAR(F190)-D190)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F190)-D190-25)/5,0)))))</f>
+        <v>Master C2</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C191" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D191" s="0" t="n">
+        <v>1983</v>
+      </c>
+      <c r="E191" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G191" s="0" t="n">
+        <v>733</v>
+      </c>
+      <c r="H191" s="1" t="str">
+        <f aca="false">IF((YEAR(F191)-D191)&lt;=11,"Avenirs",IF((YEAR(F191)-D191)&lt;=13,"Benjamins",IF((YEAR(F191)-D191)&lt;=18,"Juniors",IF((YEAR(F191)-D191)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F191)-D191-25)/5,0)))))</f>
+        <v>Master C4</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C192" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="D192" s="0" t="n">
+        <v>1993</v>
+      </c>
+      <c r="E192" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G192" s="0" t="n">
+        <v>476</v>
+      </c>
+      <c r="H192" s="1" t="str">
+        <f aca="false">IF((YEAR(F192)-D192)&lt;=11,"Avenirs",IF((YEAR(F192)-D192)&lt;=13,"Benjamins",IF((YEAR(F192)-D192)&lt;=18,"Juniors",IF((YEAR(F192)-D192)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F192)-D192-25)/5,0)))))</f>
+        <v>Master C2</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C193" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="D193" s="0" t="n">
+        <v>1993</v>
+      </c>
+      <c r="E193" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G193" s="0" t="n">
+        <v>512</v>
+      </c>
+      <c r="H193" s="1" t="str">
+        <f aca="false">IF((YEAR(F193)-D193)&lt;=11,"Avenirs",IF((YEAR(F193)-D193)&lt;=13,"Benjamins",IF((YEAR(F193)-D193)&lt;=18,"Juniors",IF((YEAR(F193)-D193)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F193)-D193-25)/5,0)))))</f>
+        <v>Master C2</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C194" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D194" s="0" t="n">
+        <v>1996</v>
+      </c>
+      <c r="E194" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="F194" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G194" s="0" t="n">
+        <v>358</v>
+      </c>
+      <c r="H194" s="1" t="str">
+        <f aca="false">IF((YEAR(F194)-D194)&lt;=11,"Avenirs",IF((YEAR(F194)-D194)&lt;=13,"Benjamins",IF((YEAR(F194)-D194)&lt;=18,"Juniors",IF((YEAR(F194)-D194)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F194)-D194-25)/5,0)))))</f>
+        <v>Master C1</v>
+      </c>
     </row>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -5847,19 +6422,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
